--- a/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,413 +656,426 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45200</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45109</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45018</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44927</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44836</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44745</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>742600</v>
+      </c>
+      <c r="E8" s="3">
         <v>744000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>665100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>846100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>866500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>783800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>613400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1002300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>636900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>509700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>176600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>375300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>809200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>476100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>201800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>174700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>152200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>126500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>108300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>148000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>132600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>117400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>103200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>169100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>114900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>50900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>38300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>73700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>52800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>361300</v>
+      </c>
+      <c r="E9" s="3">
         <v>375900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>368700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>397500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>417500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>376300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>275900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>522600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>147500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>136300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>70400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>73400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>107700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>92400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>53000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>59700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>57300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>50600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>49100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>57000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>50500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>47800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>45500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>62900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>60900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>17800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>381300</v>
+      </c>
+      <c r="E10" s="3">
         <v>368100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>296400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>448600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>449000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>407500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>337500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>479700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>489400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>373400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>106200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>301900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>701500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>383700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>148800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>115000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>94900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>75900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>59200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>91000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>82100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>69600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>57700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>106200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>54000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>31500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>20500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>50100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>33700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1095,100 +1108,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E12" s="3">
         <v>62400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>62800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>62300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>64300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>65600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>21400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>21000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>11700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>13100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1279,126 +1296,132 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E14" s="3">
         <v>26500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>24200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>29700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>26400</v>
       </c>
       <c r="H14" s="3">
         <v>26400</v>
       </c>
       <c r="I14" s="3">
+        <v>26400</v>
+      </c>
+      <c r="J14" s="3">
         <v>104200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>7300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>8000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>9500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2400</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>51400</v>
+        <v>51200</v>
       </c>
       <c r="E15" s="3">
         <v>51400</v>
       </c>
       <c r="F15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="G15" s="3">
         <v>50800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>53900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>50500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7100</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>10</v>
@@ -1412,8 +1435,8 @@
       <c r="O15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1430,8 +1453,8 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>10</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>10</v>
@@ -1448,14 +1471,14 @@
       <c r="AA15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC15" s="3">
         <v>2500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2400</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>2300</v>
       </c>
       <c r="AE15" s="3">
         <v>2300</v>
@@ -1463,8 +1486,11 @@
       <c r="AF15" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1494,192 +1520,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>702500</v>
+      </c>
+      <c r="E17" s="3">
         <v>717700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>692000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>746500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>780000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>727000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>557700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>381600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>260100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>227900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>153300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>151100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>192100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>178500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>118100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>123000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>117100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>105800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>103200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>116800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>105100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>101800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>105100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>122600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>111000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>53400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>49300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>54500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>46900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E18" s="3">
         <v>26300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-26900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>99600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>86500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>56800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>55700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>620700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>376800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>281800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>224200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>617100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>297600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>83700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>51700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>35100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>31200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>27600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>15600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>46500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>19200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1712,32 +1745,33 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>5700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3900</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1757,11 +1791,11 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1804,177 +1838,183 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>153200</v>
+      </c>
+      <c r="E21" s="3">
         <v>145100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>95600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>216400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>195800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>164900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>97800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>637500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>391100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>294600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>37800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>236900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>629400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>310000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>94400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>64100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>50100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>33000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>43100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>39500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>26300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>58600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>16800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>24900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>11100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E22" s="3">
         <v>47500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>45500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>42200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>38100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>29400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4600</v>
-      </c>
-      <c r="W22" s="3">
-        <v>4800</v>
       </c>
       <c r="X22" s="3">
         <v>4800</v>
       </c>
       <c r="Y22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Z22" s="3">
         <v>6800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>9200</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>2800</v>
       </c>
       <c r="AC22" s="3">
         <v>2800</v>
@@ -1983,197 +2023,206 @@
         <v>2800</v>
       </c>
       <c r="AE22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AF22" s="3">
         <v>3100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-64400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>60000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>41100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>31300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>42900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>620600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>375400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>281500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>221800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>615500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>295800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>80200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>48800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>32500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>17500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>26600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>22700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>38700</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>-5300</v>
       </c>
       <c r="AB23" s="3">
         <v>-5300</v>
       </c>
       <c r="AC23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-13800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>16400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-11200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>23600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>140700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>84100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>65700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>43700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>145400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>63500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-9700</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2264,192 +2313,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-53200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>48800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>479900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>291300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>215800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>178100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>470100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>232300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>67700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>40200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>30600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>24800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>32500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>10800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>34000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>14300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-53200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>48800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>30300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>19200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>479900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>291300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>215800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>178100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>470100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>232300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>67700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>40200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>30600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>32500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>10800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>34000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>14300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2540,8 +2598,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2632,8 +2693,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2724,8 +2788,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2816,32 +2883,35 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3900</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2861,11 +2931,11 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2908,100 +2978,106 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-53200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>48800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>30300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>19200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>479900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>291300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>215800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>178100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>470100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>232300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>67700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>40200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>30600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>32500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>10800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>34000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>14300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3092,197 +3168,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-53200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>48800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>30300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>19200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>479900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>291300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>215800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>178100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>470100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>232300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>67700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>40200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>30600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>32500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>10800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>34000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>14300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45200</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45109</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45018</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44927</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44836</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44745</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3315,8 +3400,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3349,129 +3435,133 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>118900</v>
+      </c>
+      <c r="E41" s="3">
         <v>149300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>178600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>353900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>292900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>212200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>379000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1275500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>802800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>578400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>593200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>981100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>489900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>77500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>72600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>108800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>52800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>28900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>28600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>56900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>43700</v>
-      </c>
-      <c r="X41" s="3">
-        <v>38700</v>
       </c>
       <c r="Y41" s="3">
         <v>38700</v>
       </c>
       <c r="Z41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="AA41" s="3">
         <v>101800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>36100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>173000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>175000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>197500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>169500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E42" s="3">
         <v>43900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>45100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>42800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>52100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>51800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>52500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>44300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25800</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>10</v>
@@ -3488,8 +3578,8 @@
       <c r="Q42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3533,405 +3623,420 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>454200</v>
+      </c>
+      <c r="E43" s="3">
         <v>520200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>426600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>454700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>542100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>557100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>514700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>590000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>393800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>350600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>85600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>105500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>529200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>376100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>120400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>110800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>104900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>86700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>57100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>81100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>76900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>91700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>44700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>92300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>67000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>41600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>19800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>20900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>25000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>577800</v>
+      </c>
+      <c r="E44" s="3">
         <v>551700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>542200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>528600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>524100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>536200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>552700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>181400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>198800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>197000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>218500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>174700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>113800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>95200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>92600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>58700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>58100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>61700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>64600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>66600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>67400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>63300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>59700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>58000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>67100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>23400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>23000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>22500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>26000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>111200</v>
+      </c>
+      <c r="E45" s="3">
         <v>106200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>115600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>118900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>163900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>87900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>60200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>23000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>20300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>9500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>24900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>16000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>161000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1310500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1371300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1308100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1498900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1575100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1445200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1559100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2113700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1440300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1149100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>917700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1282700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1142400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>560900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>296900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>286500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>222200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>185400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>157500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>211600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>193400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>200100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>168000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>268000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>331200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>244500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>225300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>244900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>225400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E47" s="3">
         <v>11900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>24700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>33800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>21000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>20300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>15200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>37900</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>10</v>
@@ -3948,8 +4053,8 @@
       <c r="Q47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3993,61 +4098,64 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1613400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1541600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1553600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1541100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1520000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1425300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1279000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>489300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>476800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>452200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>385900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>307100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>211000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>189800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>172600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>170400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>171900</v>
-      </c>
-      <c r="T48" s="3">
-        <v>161300</v>
       </c>
       <c r="U48" s="3">
         <v>161300</v>
@@ -4056,129 +4164,135 @@
         <v>161300</v>
       </c>
       <c r="W48" s="3">
+        <v>161300</v>
+      </c>
+      <c r="X48" s="3">
         <v>73900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>70200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>66500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>62900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>61600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>50000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>51000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>49900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>50900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5426300</v>
+      </c>
+      <c r="E49" s="3">
         <v>5419400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5506600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5569800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5600600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5581600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5784500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>428600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>435700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>442700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>446600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>453200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>459500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>465300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>471500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>478300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>485100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>491500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>498200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>505100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>512100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>519000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>526000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>533000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>540900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>118800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>121500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>109100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>111500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4269,8 +4383,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4361,100 +4478,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>205500</v>
+      </c>
+      <c r="E52" s="3">
         <v>194900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>157300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>143500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>139100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>183100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>184600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>39700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>62400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>57500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>54400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>58300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>33300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31900</v>
-      </c>
-      <c r="R52" s="3">
-        <v>31600</v>
       </c>
       <c r="S52" s="3">
         <v>31600</v>
       </c>
       <c r="T52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="U52" s="3">
         <v>29400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>29200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>27800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>27000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4545,100 +4668,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8563100</v>
+      </c>
+      <c r="E54" s="3">
         <v>8539100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8550300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8787100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8855800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8655500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8822400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3093100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2430400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2106400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1807700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2097400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1871200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1249400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>972900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>966800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>910900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>867500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>846200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>905900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>806400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>793900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>763500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>865600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>935300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>413800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>398500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>404500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>388300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>376500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4671,8 +4800,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4705,123 +4835,127 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>294800</v>
+      </c>
+      <c r="E57" s="3">
         <v>253000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>225900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>241500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>283300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>241800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>247300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>157500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>82700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>99600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>82100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>86300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>49400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>37500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>26700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>30400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>26800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>25200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>25700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>21700</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>27300</v>
       </c>
       <c r="AA57" s="3">
         <v>27300</v>
       </c>
       <c r="AB57" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AC57" s="3">
         <v>15700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>16000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>139800</v>
+      </c>
+      <c r="E58" s="3">
         <v>193000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>207400</v>
-      </c>
-      <c r="F58" s="3">
-        <v>207500</v>
       </c>
       <c r="G58" s="3">
         <v>207500</v>
       </c>
       <c r="H58" s="3">
+        <v>207500</v>
+      </c>
+      <c r="I58" s="3">
         <v>207600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>207800</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>10</v>
@@ -4835,47 +4969,47 @@
       <c r="N58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>6700</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>12800</v>
       </c>
       <c r="R58" s="3">
         <v>12800</v>
       </c>
       <c r="S58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="T58" s="3">
         <v>13100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>12900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>55400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>54400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>53900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>53400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>94700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>20200</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>100</v>
       </c>
       <c r="AC58" s="3">
         <v>100</v>
@@ -4887,218 +5021,227 @@
         <v>100</v>
       </c>
       <c r="AF58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG58" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>399200</v>
+      </c>
+      <c r="E59" s="3">
         <v>414000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>356700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>458800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>516200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>423300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>444900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>335200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>222000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>214400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>109700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>284800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>250600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>151800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>132700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>90300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>86100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>75600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>74400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>77400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>80200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>78900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>77200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>75300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>80900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>23200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>20000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>18600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>833800</v>
+      </c>
+      <c r="E60" s="3">
         <v>860000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>790000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>907800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1007000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>872700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>900000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>492700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>323500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>297100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>209300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>366900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>337000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>207900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>183000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>136200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>125900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>127200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>112100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>159600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>159700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>158400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>152300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>197300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>128300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>38900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>31300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>29100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>33600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2274800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2274600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2308500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2379600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2430800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2482000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2533300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -5124,141 +5267,147 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>4400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>22800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>37900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>53200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>83200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>81000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>132200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>377300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>152400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>151000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>149700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>148300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>448600</v>
+      </c>
+      <c r="E62" s="3">
         <v>437800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>449300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>503200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>483400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>505500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>469500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>185500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>177500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>175200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>187300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>240700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>201500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>192200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>178200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>225400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>220800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>201700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>201300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>247700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>167900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>163800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>161300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>205500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>202500</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>3600</v>
       </c>
       <c r="AC62" s="3">
         <v>3600</v>
       </c>
       <c r="AD62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AE62" s="3">
         <v>5600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5349,8 +5498,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5441,8 +5593,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5533,100 +5688,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3557200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3572400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3547800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3790600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3921200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3860200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3902800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>678200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>501000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>472300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>396600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>607700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>538500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>400100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>361200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>361600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>351000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>333400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>336200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>445200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>380800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>405400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>394600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>535000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>708100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>194900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>185900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>184400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>187600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5659,8 +5820,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5751,8 +5913,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5843,8 +6008,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5935,8 +6103,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6027,100 +6198,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2187800</v>
+      </c>
+      <c r="E72" s="3">
         <v>2180800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2193500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2246700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2197900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2167600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2148400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2129100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1649200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1357900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1142100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1123100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>945000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>474800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>242600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>174900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>134700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>104100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>87900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>86600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>61800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>29300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>21500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-7300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6211,8 +6388,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6303,8 +6483,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6395,100 +6578,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5005900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4966700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5002500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4996500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4934600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4795300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4919600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2414900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1929400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1634100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1411100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1489700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1332700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>849200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>611700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>605200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>559800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>534200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>510000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>460700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>425600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>388500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>368900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>330600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>227100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>218900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>212600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>220100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>200600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>196700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6579,197 +6768,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45200</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45109</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45018</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44927</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44836</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44745</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-53200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>48800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>30300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>19200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>479900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>291300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>215800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>178100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>470100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>232300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>67700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>40200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>30600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>32500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>10800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>34000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>14300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6802,100 +7000,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E83" s="3">
         <v>113100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>114500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>114200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>116600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>104200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>46000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>16800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>15100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>11500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>6200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5700</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>5200</v>
       </c>
       <c r="AF83" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6986,8 +7188,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7078,8 +7283,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7170,8 +7378,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7262,8 +7473,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7354,100 +7568,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E89" s="3">
         <v>41500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-30600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>188900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>169400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>224600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>501000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>321400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>77100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-178000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>585500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>439100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>70500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>59000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>61200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>47700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>13300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>40500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>32900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>43200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>50600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>35800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>11200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>29600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>16600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7480,100 +7700,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-43400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-51300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-66000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-61700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-106900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-75200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-78300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-28800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-22700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4900</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-4700</v>
       </c>
       <c r="AB91" s="3">
         <v>-4700</v>
       </c>
       <c r="AC91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7664,8 +7888,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7756,100 +7983,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-55100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-42300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-68900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-59300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1530400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-96000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-93200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-65700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-64600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>141700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-404600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7882,8 +8115,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7974,8 +8208,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8066,8 +8303,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8158,8 +8398,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8250,168 +8493,174 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-57800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-48700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-99700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-59600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-31700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-126000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>413100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-144300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-29600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-43200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-87700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-62100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-14700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-29600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-105200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-111800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>256500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>9900</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>2100</v>
       </c>
       <c r="AD100" s="3">
         <v>2100</v>
       </c>
       <c r="AE100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AF100" s="3">
         <v>3600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2300</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
       <c r="W101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>200</v>
       </c>
       <c r="Y101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -8434,96 +8683,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-29700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-175300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>61000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>80700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-167400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-895000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>472800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>224300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-387800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>491100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>412400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-36200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>56000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>23900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-28400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5000</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-63100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>65700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-136900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-22400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>28000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>16100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
@@ -656,426 +656,439 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45200</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45109</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45018</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44927</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44836</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44745</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>711000</v>
+      </c>
+      <c r="E8" s="3">
         <v>742600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>744000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>665100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>846100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>866500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>783800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>613400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1002300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>636900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>509700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>176600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>375300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>809200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>476100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>201800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>174700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>152200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>126500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>108300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>148000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>132600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>117400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>103200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>169100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>114900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>50900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>38300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>73700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>52800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>378900</v>
+      </c>
+      <c r="E9" s="3">
         <v>361300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>375900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>368700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>397500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>417500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>376300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>275900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>522600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>147500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>136300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>70400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>73400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>107700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>92400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>53000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>59700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>57300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>50600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>49100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>57000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>50500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>47800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>45500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>62900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>60900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>19400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>19100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>332100</v>
+      </c>
+      <c r="E10" s="3">
         <v>381300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>368100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>296400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>448600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>449000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>407500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>337500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>479700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>489400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>373400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>106200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>301900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>701500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>383700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>148800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>115000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>94900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>75900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>59200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>91000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>82100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>69600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>57700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>106200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>54000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>31500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>20500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>50100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>33700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1109,103 +1122,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E12" s="3">
         <v>59300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>62400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>62800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>62300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>64300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>65600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>34200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>21400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>21000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>16400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>11700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>13300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>12600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1299,132 +1316,138 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>1766500</v>
+      </c>
+      <c r="E14" s="3">
         <v>33000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>26500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>24200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>29700</v>
-      </c>
-      <c r="H14" s="3">
-        <v>26400</v>
       </c>
       <c r="I14" s="3">
         <v>26400</v>
       </c>
       <c r="J14" s="3">
+        <v>26400</v>
+      </c>
+      <c r="K14" s="3">
         <v>104200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7800</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>10800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>7300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>9500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2400</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E15" s="3">
         <v>51200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>51400</v>
       </c>
       <c r="F15" s="3">
         <v>51400</v>
       </c>
       <c r="G15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="H15" s="3">
         <v>50800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>53900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>50500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7100</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>10</v>
@@ -1438,8 +1461,8 @@
       <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1456,8 +1479,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>10</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>10</v>
@@ -1474,14 +1497,14 @@
       <c r="AB15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD15" s="3">
         <v>2500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2400</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>2300</v>
       </c>
       <c r="AF15" s="3">
         <v>2300</v>
@@ -1489,8 +1512,11 @@
       <c r="AG15" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1521,198 +1547,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2469000</v>
+      </c>
+      <c r="E17" s="3">
         <v>702500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>717700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>692000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>746500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>780000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>727000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>557700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>381600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>260100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>227900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>153300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>151100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>192100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>178500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>118100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>123000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>117100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>105800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>103200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>116800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>105100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>101800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>105100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>122600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>111000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>53400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>49300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>54500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>46900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1758000</v>
+      </c>
+      <c r="E18" s="3">
         <v>40100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>26300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-26900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>99600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>86500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>56800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>55700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>620700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>376800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>281800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>23300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>224200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>617100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>297600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>83700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>51700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>35100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>31200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>27600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>15600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>46500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>19200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1746,35 +1779,36 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3900</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1794,11 +1828,11 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1841,183 +1875,189 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1636900</v>
+      </c>
+      <c r="E21" s="3">
         <v>153200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>145100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>95600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>216400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>195800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>164900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>97800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>637500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>391100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>294600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>37800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>236900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>629400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>310000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>94400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>64100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>50100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>33000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>17600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>43100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>39500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>26300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>58600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>16800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>24900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>11100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E22" s="3">
         <v>47000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>47500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>45500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>42200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>38100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>29400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4600</v>
-      </c>
-      <c r="X22" s="3">
-        <v>4800</v>
       </c>
       <c r="Y22" s="3">
         <v>4800</v>
       </c>
       <c r="Z22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AA22" s="3">
         <v>6800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>7900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9200</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>2800</v>
       </c>
       <c r="AD22" s="3">
         <v>2800</v>
@@ -2026,203 +2066,212 @@
         <v>2800</v>
       </c>
       <c r="AF22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AG22" s="3">
         <v>3100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1798900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-64400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>60000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>41100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>31300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>42900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>620600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>375400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>281500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>221800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>615500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>295800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>80200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>48800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>32500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>17500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>26600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>22700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>38700</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-5300</v>
       </c>
       <c r="AC23" s="3">
         <v>-5300</v>
       </c>
       <c r="AD23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-13800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>16400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-92900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-16200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-11200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>23600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>140700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>84100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>65700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>43700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>145400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>63500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2316,198 +2365,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1706000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-53200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>48800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>30300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>479900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>291300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>215800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>178100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>470100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>232300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>67700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>40200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>30600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>24800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>32500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>10800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>34000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>14300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1706000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-53200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>48800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>30300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>479900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>291300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>215800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>178100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>470100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>232300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>67700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>40200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>30600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>24800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>32500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>10800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>34000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>14300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2601,8 +2659,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2696,8 +2757,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2791,8 +2855,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2886,35 +2953,38 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E32" s="3">
         <v>2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3900</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2934,11 +3004,11 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>1100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2981,103 +3051,109 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1706000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-53200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>48800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>30300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>479900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>291300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>215800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>178100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>470100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>232300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>67700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>40200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>30600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>24800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>32500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>10800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>34000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>14300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3171,203 +3247,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1706000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-53200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>48800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>30300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>479900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>291300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>215800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>178100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>470100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>232300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>67700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>40200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>30600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>24800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>32500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>10800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>34000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>14300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45200</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45109</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45018</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44927</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44836</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44745</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3401,8 +3486,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3436,135 +3522,139 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E41" s="3">
         <v>118900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>149300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>178600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>353900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>292900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>212200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>379000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1275500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>802800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>578400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>593200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>981100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>489900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>77500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>72600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>108800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>52800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>28900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>28600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>56900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43700</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>38700</v>
       </c>
       <c r="Z41" s="3">
         <v>38700</v>
       </c>
       <c r="AA41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="AB41" s="3">
         <v>101800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>36100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>173000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>175000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>197500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>169500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>48400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>43900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>45100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>42800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>52100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>51800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>52500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>44300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>25800</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>10</v>
@@ -3581,8 +3671,8 @@
       <c r="R42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3626,420 +3716,435 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>476100</v>
+      </c>
+      <c r="E43" s="3">
         <v>454200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>520200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>426600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>454700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>542100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>557100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>514700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>590000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>393800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>350600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>85600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>105500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>529200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>376100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>120400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>110800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>104900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>86700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>57100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>81100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>76900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>91700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>44700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>92300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>67000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>41600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>19800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>20900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>25000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>583100</v>
+      </c>
+      <c r="E44" s="3">
         <v>577800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>551700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>542200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>528600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>524100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>536200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>552700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>181400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>198800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>197000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>218500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>174700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>113800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>95200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>92600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>58700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>58100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>61700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>64600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>66600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>67400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>63300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>59700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>58000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>67100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>23400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>23000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>22500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>26000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E45" s="3">
         <v>111200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>106200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>115600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>118900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>163900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>87900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>60200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>20300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>24900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>16000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>161000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1212400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1310500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1371300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1308100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1498900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1575100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1445200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1559100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2113700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1440300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1149100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>917700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1282700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1142400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>560900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>296900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>286500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>222200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>185400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>157500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>211600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>193400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>200100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>168000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>268000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>331200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>244500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>225300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>244900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>225400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
         <v>7400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>24700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>33800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>21000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>15200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>37900</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>10</v>
@@ -4056,8 +4161,8 @@
       <c r="R47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -4101,64 +4206,67 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1621800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1613400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1541600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1553600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1541100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1520000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1425300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1279000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>489300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>476800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>452200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>385900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>307100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>211000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>189800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>172600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>170400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>171900</v>
-      </c>
-      <c r="U48" s="3">
-        <v>161300</v>
       </c>
       <c r="V48" s="3">
         <v>161300</v>
@@ -4167,132 +4275,138 @@
         <v>161300</v>
       </c>
       <c r="X48" s="3">
+        <v>161300</v>
+      </c>
+      <c r="Y48" s="3">
         <v>73900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>70200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>66500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>62900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>61600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>50000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>51000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>49900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>50900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3622100</v>
+      </c>
+      <c r="E49" s="3">
         <v>5426300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5419400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5506600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5569800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5600600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5581600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5784500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>428600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>435700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>442700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>446600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>453200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>459500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>465300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>471500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>478300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>485100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>491500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>498200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>505100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>512100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>519000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>526000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>533000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>540900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>118800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>121500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>109100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>111500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4386,8 +4500,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,103 +4598,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E52" s="3">
         <v>205500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>194900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>157300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>143500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>139100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>183100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>184600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>40800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>39700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>62400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>57500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>54400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>58300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>33300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>31900</v>
-      </c>
-      <c r="S52" s="3">
-        <v>31600</v>
       </c>
       <c r="T52" s="3">
         <v>31600</v>
       </c>
       <c r="U52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="V52" s="3">
         <v>29400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>29200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>27800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>27000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4671,103 +4794,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6703300</v>
+      </c>
+      <c r="E54" s="3">
         <v>8563100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8539100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8550300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8787100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8855800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8655500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8822400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3093100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2430400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2106400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1807700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2097400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1871200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1249400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>972900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>966800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>910900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>867500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>846200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>905900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>806400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>793900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>763500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>865600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>935300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>413800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>398500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>404500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>388300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>376500</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4801,8 +4930,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4836,129 +4966,133 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>249600</v>
+      </c>
+      <c r="E57" s="3">
         <v>294800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>253000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>225900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>241500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>283300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>241800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>247300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>157500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>101500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>82700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>99600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>82100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>86300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>49400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>37500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>26700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>30400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>24800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>26800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>25200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>25700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>21700</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>27300</v>
       </c>
       <c r="AB57" s="3">
         <v>27300</v>
       </c>
       <c r="AC57" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AD57" s="3">
         <v>15700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>16000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>161100</v>
+      </c>
+      <c r="E58" s="3">
         <v>139800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>193000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>207400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>207500</v>
       </c>
       <c r="H58" s="3">
         <v>207500</v>
       </c>
       <c r="I58" s="3">
+        <v>207500</v>
+      </c>
+      <c r="J58" s="3">
         <v>207600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>207800</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>10</v>
@@ -4972,47 +5106,47 @@
       <c r="O58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>6700</v>
-      </c>
-      <c r="R58" s="3">
-        <v>12800</v>
       </c>
       <c r="S58" s="3">
         <v>12800</v>
       </c>
       <c r="T58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="U58" s="3">
         <v>13100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>21200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>12900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>55400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>54400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>53900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>53400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>94700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>20200</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>100</v>
       </c>
       <c r="AD58" s="3">
         <v>100</v>
@@ -5024,227 +5158,236 @@
         <v>100</v>
       </c>
       <c r="AG58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH58" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>369100</v>
+      </c>
+      <c r="E59" s="3">
         <v>399200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>414000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>356700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>458800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>516200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>423300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>444900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>335200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>222000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>214400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>109700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>284800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>250600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>151800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>132700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>90300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>86100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>75600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>74400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>77400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>80200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>78900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>77200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>75300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>80900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>23200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>20000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>18600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>17500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>779800</v>
+      </c>
+      <c r="E60" s="3">
         <v>833800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>860000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>790000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>907800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1007000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>872700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>900000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>492700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>323500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>297100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>209300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>366900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>337000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>207900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>183000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>136200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>125900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>127200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>112100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>159600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>159700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>158400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>152300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>197300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>128300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>38900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>31300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>29100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>33600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2241000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2274800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2274600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2308500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2379600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2430800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2482000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2533300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5270,144 +5413,150 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>4400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>22800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>37900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>53200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>83200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>81000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>132200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>377300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>152400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>151000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>149700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>148300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>374800</v>
+      </c>
+      <c r="E62" s="3">
         <v>448600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>437800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>449300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>503200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>483400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>505500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>469500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>185500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>177500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>175200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>187300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>240700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>201500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>192200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>178200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>225400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>220800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>201700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>201300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>247700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>167900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>163800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>161300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>205500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>202500</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>3600</v>
       </c>
       <c r="AD62" s="3">
         <v>3600</v>
       </c>
       <c r="AE62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AF62" s="3">
         <v>5600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5501,8 +5650,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5596,8 +5748,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5691,103 +5846,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3395600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3557200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3572400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3547800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3790600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3921200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3860200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3902800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>678200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>501000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>472300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>396600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>607700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>538500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>400100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>361200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>361600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>351000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>333400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>336200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>445200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>380800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>405400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>394600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>535000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>708100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>194900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>185900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>184400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>187600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5821,8 +5982,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5916,8 +6078,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6011,8 +6176,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6106,8 +6274,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6201,103 +6372,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>481800</v>
+      </c>
+      <c r="E72" s="3">
         <v>2187800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2180800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2193500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2246700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2197900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2167600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2148400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2129100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1649200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1357900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1142100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1123100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>945000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>474800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>242600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>174900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>134700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>104100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>87900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>86600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>61800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>29300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>21500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6391,8 +6568,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6486,8 +6666,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6581,103 +6764,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3307700</v>
+      </c>
+      <c r="E76" s="3">
         <v>5005900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4966700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5002500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4996500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4934600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4795300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4919600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2414900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1929400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1634100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1411100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1489700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1332700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>849200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>611700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>605200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>559800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>534200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>510000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>460700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>425600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>388500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>368900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>330600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>227100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>218900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>212600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>220100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>200600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>196700</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6771,203 +6960,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45200</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45109</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45018</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44927</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44836</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44745</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1706000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-53200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>48800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>30300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>479900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>291300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>215800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>178100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>470100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>232300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>67700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>40200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>30600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>24800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>32500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>10800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>34000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>14300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7001,103 +7199,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E83" s="3">
         <v>115400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>113100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>114500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>114200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>116600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>104200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>46000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>16800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>15100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>11900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>6200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5700</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>5200</v>
       </c>
       <c r="AG83" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7191,8 +7393,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7286,8 +7491,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7381,8 +7589,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7476,8 +7687,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7571,103 +7785,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>80400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>41500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>188900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>169400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>224600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>501000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>321400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>77100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-178000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>585500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>439100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>70500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>59000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>61200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>47700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>13300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>40500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>32900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>43200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>50600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>35800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>29600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>16600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7701,103 +7921,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-66100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-48600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-43400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-51300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-66000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-61700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-106900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-75200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-78300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-28800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-22700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4900</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-4700</v>
       </c>
       <c r="AC91" s="3">
         <v>-4700</v>
       </c>
       <c r="AD91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7891,8 +8115,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7986,103 +8213,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-55100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-68900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-59300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1530400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-24700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-96000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-93200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-65700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-64600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-27200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>141700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-404600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8116,8 +8349,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8211,8 +8445,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8306,8 +8543,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8401,8 +8641,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8496,174 +8739,180 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-57800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-48700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-99700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-59600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-31700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-126000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>413100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-144300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-29600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-43200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-87700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-15500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-62100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-14700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-29600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-105200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-111800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>256500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>9900</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>2100</v>
       </c>
       <c r="AE100" s="3">
         <v>2100</v>
       </c>
       <c r="AF100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AG100" s="3">
         <v>3600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>2100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2300</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>-100</v>
       </c>
       <c r="M101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
       <c r="X101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Y101" s="3">
         <v>200</v>
       </c>
       <c r="Z101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -8686,99 +8935,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-30400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-29700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-175300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>61000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>80700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-167400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-895000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>472800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>224300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-387800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>491100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>412400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-36200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>56000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>23900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-28400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5000</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-63100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>65700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-136900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-22400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>28000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>16100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
@@ -656,439 +656,452 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45200</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45109</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45018</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44927</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44836</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44745</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>637000</v>
+      </c>
+      <c r="E8" s="3">
         <v>711000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>742600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>744000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>665100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>846100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>866500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>783800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>613400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1002300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>636900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>509700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>176600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>375300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>809200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>476100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>201800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>174700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>152200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>126500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>108300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>148000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>132600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>117400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>103200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>169100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>114900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>50900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>38300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>73700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>52800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E9" s="3">
         <v>378900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>361300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>375900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>368700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>397500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>417500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>376300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>275900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>522600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>147500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>136300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>70400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>73400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>107700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>92400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>53000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>59700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>57300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>50600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>49100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>57000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>50500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>47800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>45500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>62900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>60900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>19400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>17800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>19100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E10" s="3">
         <v>332100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>381300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>368100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>296400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>448600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>449000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>407500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>337500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>479700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>489400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>373400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>106200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>301900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>701500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>383700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>148800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>115000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>94900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>75900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>59200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>91000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>82100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>69600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>57700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>106200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>54000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>31500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>20500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>50100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>33700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1123,106 +1136,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E12" s="3">
         <v>59200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>59300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>62400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>62800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>62300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>64300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>65600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>34200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>25500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>21400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>16400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>11700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>13900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>13100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>13300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>10700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1319,138 +1336,144 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E14" s="3">
         <v>1766500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>33000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>26500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>24200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>29700</v>
-      </c>
-      <c r="I14" s="3">
-        <v>26400</v>
       </c>
       <c r="J14" s="3">
         <v>26400</v>
       </c>
       <c r="K14" s="3">
+        <v>26400</v>
+      </c>
+      <c r="L14" s="3">
         <v>104200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7800</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>10800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>7300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>8000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>9500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>4600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2400</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E15" s="3">
         <v>51700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>51200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>51400</v>
       </c>
       <c r="G15" s="3">
         <v>51400</v>
       </c>
       <c r="H15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="I15" s="3">
         <v>50800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>53900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>50500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7100</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>10</v>
@@ -1464,8 +1487,8 @@
       <c r="Q15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1482,8 +1505,8 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>10</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>10</v>
@@ -1500,14 +1523,14 @@
       <c r="AC15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE15" s="3">
         <v>2500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2400</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>2300</v>
       </c>
       <c r="AG15" s="3">
         <v>2300</v>
@@ -1515,8 +1538,11 @@
       <c r="AH15" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1548,204 +1574,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>754500</v>
+      </c>
+      <c r="E17" s="3">
         <v>2469000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>702500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>717700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>692000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>746500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>780000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>727000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>557700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>381600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>260100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>227900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>153300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>151100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>192100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>178500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>118100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>123000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>117100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>105800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>103200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>116800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>105100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>101800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>105100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>122600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>111000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>53400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>49300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>54500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>46900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-117500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1758000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>40100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>26300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-26900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>99600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>86500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>56800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>55700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>620700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>376800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>281800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>23300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>224200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>617100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>297600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>83700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>51700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>35100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>20700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>31200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>27600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>15600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>46500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>19200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>5900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1780,38 +1813,39 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E20" s="3">
         <v>6200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>8000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3900</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1831,11 +1865,11 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1878,189 +1912,195 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1636900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>153200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>145100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>95600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>216400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>195800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>164900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>97800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>637500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>391100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>294600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>37800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>236900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>629400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>310000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>94400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>64100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>50100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>33000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>17600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>43100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>39500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>26300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>58600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>16800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>24900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>11100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E22" s="3">
         <v>47100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>47000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>47500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>45500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>42200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>29400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4600</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>4800</v>
       </c>
       <c r="Z22" s="3">
         <v>4800</v>
       </c>
       <c r="AA22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AB22" s="3">
         <v>6800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9200</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>2800</v>
       </c>
       <c r="AE22" s="3">
         <v>2800</v>
@@ -2069,209 +2109,218 @@
         <v>2800</v>
       </c>
       <c r="AG22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AH22" s="3">
         <v>3100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-162900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1798900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-64400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>60000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>41100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>42900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>620600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>375400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>281500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>221800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>615500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>295800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>80200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>48800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>32500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>17500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>26600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>22700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>38700</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-5300</v>
       </c>
       <c r="AD23" s="3">
         <v>-5300</v>
       </c>
       <c r="AE23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-13800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>16400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-92900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-16200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-11200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>23600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>140700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>84100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>65700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>43700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>145400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>63500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>12500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2368,204 +2417,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-147700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1706000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-53200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>48800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>30300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>479900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>291300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>215800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>178100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>470100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>232300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>67700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>40200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>30600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>24800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>32500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>10800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>34000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>14300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-147700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1706000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-53200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>48800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>30300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>479900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>291300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>215800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>178100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>470100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>232300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>67700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>40200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>30600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>24800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>32500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>10800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>34000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>14300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2662,8 +2720,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2760,8 +2821,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2858,8 +2922,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2956,38 +3023,41 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-8000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3900</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -3007,11 +3077,11 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>1100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3054,106 +3124,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-147700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1706000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-53200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>48800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>30300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>479900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>291300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>215800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>178100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>470100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>232300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>67700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>40200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>30600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>24800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>32500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>10800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>34000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>14300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3250,209 +3326,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-147700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1706000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-53200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>48800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>30300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>479900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>291300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>215800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>178100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>470100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>232300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>67700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>40200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>30600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>24800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>32500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>10800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>34000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>14300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45200</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45109</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45018</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44927</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44836</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44745</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,8 +3572,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3523,106 +3609,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E41" s="3">
         <v>78500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>118900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>149300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>178600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>353900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>292900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>212200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>379000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1275500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>802800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>578400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>593200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>981100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>489900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>77500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>72600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>108800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>52800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>28900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>28600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>56900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43700</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>38700</v>
       </c>
       <c r="AA41" s="3">
         <v>38700</v>
       </c>
       <c r="AB41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="AC41" s="3">
         <v>101800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>36100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>173000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>175000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>197500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>169500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3630,34 +3720,34 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>48400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>43900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>45100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>42800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>52100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>51800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>52500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>44300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>25800</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>10</v>
@@ -3674,8 +3764,8 @@
       <c r="S42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3719,400 +3809,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>497300</v>
+      </c>
+      <c r="E43" s="3">
         <v>476100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>454200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>520200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>426600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>454700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>542100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>557100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>514700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>590000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>393800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>350600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>85600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>105500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>529200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>376100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>120400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>110800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>104900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>86700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>57100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>81100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>76900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>91700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>44700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>92300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>67000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>41600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>19800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>20900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>25000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>602000</v>
+      </c>
+      <c r="E44" s="3">
         <v>583100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>577800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>551700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>542200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>528600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>524100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>536200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>552700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>181400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>198800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>197000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>218500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>174700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>113800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>95200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>92600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>58700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>58100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>61700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>64600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>66600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>67400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>63300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>59700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>58000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>67100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>23400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>23000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>22500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>26000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E45" s="3">
         <v>74700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>111200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>106200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>115600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>118900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>163900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>87900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>60200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>20300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>9500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>24900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>16000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>161000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1341300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1212400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1310500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1371300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1308100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1498900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1575100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1445200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1559100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2113700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1440300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1149100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>917700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1282700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1142400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>560900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>296900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>286500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>222200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>185400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>157500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>211600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>193400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>200100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>168000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>268000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>331200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>244500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>225300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>244900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>225400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4120,34 +4225,34 @@
         <v>0</v>
       </c>
       <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
         <v>7400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>24700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>33800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>21000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>15200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>37900</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>10</v>
@@ -4164,8 +4269,8 @@
       <c r="S47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -4209,67 +4314,70 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1503900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1621800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1613400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1541600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1553600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1541100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1520000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1425300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1279000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>489300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>476800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>452200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>385900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>307100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>211000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>189800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>172600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>170400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>171900</v>
-      </c>
-      <c r="V48" s="3">
-        <v>161300</v>
       </c>
       <c r="W48" s="3">
         <v>161300</v>
@@ -4278,135 +4386,141 @@
         <v>161300</v>
       </c>
       <c r="Y48" s="3">
+        <v>161300</v>
+      </c>
+      <c r="Z48" s="3">
         <v>73900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>70200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>66500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>62900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>61600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>50000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>51000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>49900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>50900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3568500</v>
+      </c>
+      <c r="E49" s="3">
         <v>3622100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5426300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5419400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5506600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5569800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5600600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5581600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5784500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>428600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>435700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>442700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>446600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>453200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>459500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>465300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>471500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>478300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>485100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>491500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>498200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>505100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>512100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>519000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>526000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>533000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>540900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>118800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>121500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>109100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>111500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4503,8 +4617,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4601,106 +4718,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>275500</v>
+      </c>
+      <c r="E52" s="3">
         <v>247000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>205500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>194900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>157300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>143500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>139100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>183100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>184600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>40800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>39700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>62400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>57500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>54400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>58300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>33300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>31900</v>
-      </c>
-      <c r="T52" s="3">
-        <v>31600</v>
       </c>
       <c r="U52" s="3">
         <v>31600</v>
       </c>
       <c r="V52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="W52" s="3">
         <v>29400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>29200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>27800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>27000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4797,106 +4920,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6689200</v>
+      </c>
+      <c r="E54" s="3">
         <v>6703300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8563100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8539100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8550300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8787100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8855800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8655500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8822400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3093100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2430400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2106400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1807700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2097400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1871200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1249400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>972900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>966800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>910900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>867500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>846200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>905900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>806400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>793900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>763500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>865600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>935300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>413800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>398500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>404500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>388300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>376500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4931,8 +5060,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4967,135 +5097,139 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>237400</v>
+      </c>
+      <c r="E57" s="3">
         <v>249600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>294800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>253000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>225900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>241500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>283300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>241800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>247300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>157500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>101500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>82700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>99600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>82100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>86300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>49400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>37500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>33200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>26700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>30400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>24800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>26800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>25200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>25700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>21700</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>27300</v>
       </c>
       <c r="AC57" s="3">
         <v>27300</v>
       </c>
       <c r="AD57" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AE57" s="3">
         <v>15700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>16000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>356400</v>
+      </c>
+      <c r="E58" s="3">
         <v>161100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>139800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>193000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>207400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>207500</v>
       </c>
       <c r="I58" s="3">
         <v>207500</v>
       </c>
       <c r="J58" s="3">
+        <v>207500</v>
+      </c>
+      <c r="K58" s="3">
         <v>207600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>207800</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>10</v>
@@ -5109,47 +5243,47 @@
       <c r="P58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>6700</v>
-      </c>
-      <c r="S58" s="3">
-        <v>12800</v>
       </c>
       <c r="T58" s="3">
         <v>12800</v>
       </c>
       <c r="U58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="V58" s="3">
         <v>13100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>12900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>55400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>54400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>53900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>53400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>94700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>20200</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>100</v>
       </c>
       <c r="AE58" s="3">
         <v>100</v>
@@ -5161,236 +5295,245 @@
         <v>100</v>
       </c>
       <c r="AH58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI58" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>338600</v>
+      </c>
+      <c r="E59" s="3">
         <v>369100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>399200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>414000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>356700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>458800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>516200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>423300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>444900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>335200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>222000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>214400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>109700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>284800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>250600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>151800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>132700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>90300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>86100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>75600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>74400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>77400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>80200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>78900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>77200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>75300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>80900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>23200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>20000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>18600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>17500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>932400</v>
+      </c>
+      <c r="E60" s="3">
         <v>779800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>833800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>860000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>790000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>907800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1007000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>872700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>900000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>492700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>323500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>297100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>209300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>366900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>337000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>207900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>183000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>136200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>125900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>127200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>112100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>159600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>159700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>158400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>152300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>197300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>128300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>38900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>31300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>29100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>33600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2207200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2241000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2274800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2274600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2308500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2379600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2430800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2482000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2533300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5416,147 +5559,153 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>4400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>22800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>53200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>83200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>81000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>132200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>377300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>152400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>151000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>149700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>148300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>376100</v>
+      </c>
+      <c r="E62" s="3">
         <v>374800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>448600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>437800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>449300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>503200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>483400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>505500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>469500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>185500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>177500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>175200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>187300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>240700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>201500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>192200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>178200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>225400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>220800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>201700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>201300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>247700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>167900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>163800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>161300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>205500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>202500</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>3600</v>
       </c>
       <c r="AE62" s="3">
         <v>3600</v>
       </c>
       <c r="AF62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AG62" s="3">
         <v>5600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5653,8 +5802,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5751,8 +5903,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5849,106 +6004,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3515700</v>
+      </c>
+      <c r="E66" s="3">
         <v>3395600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3557200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3572400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3547800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3790600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3921200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3860200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3902800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>678200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>501000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>472300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>396600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>607700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>538500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>400100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>361200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>361600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>351000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>333400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>336200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>445200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>380800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>405400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>394600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>535000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>708100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>194900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>185900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>184400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>187600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5983,8 +6144,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6081,8 +6243,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6179,8 +6344,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6277,8 +6445,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6375,106 +6546,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>334100</v>
+      </c>
+      <c r="E72" s="3">
         <v>481800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2187800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2180800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2193500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2246700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2197900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2167600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2148400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2129100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1649200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1357900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1142100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1123100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>945000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>474800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>242600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>174900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>134700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>104100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>87900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>86600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>61800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>29300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>21500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-7300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6571,8 +6748,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6669,8 +6849,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6767,106 +6950,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3173500</v>
+      </c>
+      <c r="E76" s="3">
         <v>3307700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5005900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4966700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5002500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4996500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4934600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4795300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4919600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2414900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1929400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1634100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1411100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1489700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1332700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>849200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>611700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>605200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>559800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>534200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>510000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>460700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>425600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>388500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>368900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>330600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>227100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>218900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>212600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>220100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>200600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>196700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6963,209 +7152,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45200</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45109</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45018</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44927</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44836</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44745</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-147700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1706000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-53200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>48800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>30300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>479900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>291300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>215800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>178100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>470100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>232300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>67700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>40200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>30600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>24800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>32500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>10800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>34000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>14300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7200,106 +7398,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>116100</v>
+      </c>
+      <c r="E83" s="3">
         <v>114900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>115400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>113100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>114500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>114200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>116600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>104200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>16800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>15100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>11900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>10700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5700</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>5200</v>
       </c>
       <c r="AH83" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7396,8 +7598,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7494,8 +7699,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7592,8 +7800,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7690,8 +7901,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7788,106 +8002,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-97900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>80400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>188900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>169400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>224600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>501000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>321400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>77100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-178000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>585500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>439100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>70500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>59000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>61200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>47700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>13300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>40500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>32900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>43200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>50600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>35800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>11200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>29600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>16600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7922,106 +8142,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-35300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-48600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-43400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-51300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-66000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-61700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-30500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-106900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-75200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-78300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-28800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4900</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-4700</v>
       </c>
       <c r="AD91" s="3">
         <v>-4700</v>
       </c>
       <c r="AE91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8118,8 +8342,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8216,106 +8443,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-55100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-42300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-68900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-59300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1530400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-96000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-93200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-65700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-64600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>141700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-404600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8350,8 +8583,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8448,8 +8682,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8546,8 +8783,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8644,8 +8884,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8742,180 +8985,186 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>162500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-57800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-48700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-99700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-59600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-31700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-126000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>413100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-144300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-29600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-43200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-87700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-15500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-62100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-14700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-29600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-105200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-111800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>256500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>9900</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>2100</v>
       </c>
       <c r="AF100" s="3">
         <v>2100</v>
       </c>
       <c r="AG100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AH100" s="3">
         <v>3600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-100</v>
       </c>
       <c r="M101" s="3">
         <v>-100</v>
       </c>
       <c r="N101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
       <c r="Y101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z101" s="3">
         <v>200</v>
       </c>
       <c r="AA101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -8938,102 +9187,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-40500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-29700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-175300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>61000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>80700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-167400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-895000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>472800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>224300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-387800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>491100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>412400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-36200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>56000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>23900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-28400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5000</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>-63100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>65700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-136900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-22400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>28000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>16100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>QDEL</t>
   </si>
@@ -656,452 +656,465 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45200</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45109</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45018</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44927</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44836</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44745</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>727100</v>
+      </c>
+      <c r="E8" s="3">
         <v>637000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>711000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>742600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>744000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>665100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>846100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>866500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>783800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>613400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1002300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>636900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>509700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>176600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>375300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>809200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>476100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>201800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>174700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>152200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>126500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>108300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>148000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>132600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>117400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>103200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>169100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>114900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>50900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>38300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>73700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>52800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>374800</v>
+      </c>
+      <c r="E9" s="3">
         <v>361000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>378900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>361300</v>
       </c>
-      <c r="G9" s="3">
-        <v>375900</v>
-      </c>
       <c r="H9" s="3">
-        <v>368700</v>
+        <v>374600</v>
       </c>
       <c r="I9" s="3">
+        <v>368600</v>
+      </c>
+      <c r="J9" s="3">
         <v>397500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>417500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>376300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>275900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>522600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>147500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>136300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>70400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>73400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>107700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>92400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>53000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>59700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>57300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>50600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>49100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>57000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>50500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>47800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>45500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>62900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>60900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>17800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>23600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>19100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>352300</v>
+      </c>
+      <c r="E10" s="3">
         <v>276000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>332100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>381300</v>
       </c>
-      <c r="G10" s="3">
-        <v>368100</v>
-      </c>
       <c r="H10" s="3">
-        <v>296400</v>
+        <v>369400</v>
       </c>
       <c r="I10" s="3">
+        <v>296500</v>
+      </c>
+      <c r="J10" s="3">
         <v>448600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>449000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>407500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>337500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>479700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>489400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>373400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>106200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>301900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>701500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>383700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>148800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>115000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>94900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>75900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>59200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>91000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>82100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>69600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>57700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>106200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>54000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>31500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>20500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>50100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>33700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1137,109 +1150,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E12" s="3">
         <v>56300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>59200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>59300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>61500</v>
+      </c>
+      <c r="I12" s="3">
         <v>62400</v>
       </c>
-      <c r="H12" s="3">
-        <v>62800</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>62300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>64300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>65600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>34200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>22600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>23300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>21400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>21000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>16400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>14900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>11700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>13100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>13300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>12600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>7500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1339,109 +1356,115 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E14" s="3">
         <v>87800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1766500</v>
       </c>
-      <c r="F14" s="3">
-        <v>33000</v>
-      </c>
       <c r="G14" s="3">
-        <v>26500</v>
+        <v>60100</v>
       </c>
       <c r="H14" s="3">
-        <v>24200</v>
+        <v>28700</v>
       </c>
       <c r="I14" s="3">
+        <v>24700</v>
+      </c>
+      <c r="J14" s="3">
         <v>29700</v>
-      </c>
-      <c r="J14" s="3">
-        <v>26400</v>
       </c>
       <c r="K14" s="3">
         <v>26400</v>
       </c>
       <c r="L14" s="3">
+        <v>26400</v>
+      </c>
+      <c r="M14" s="3">
         <v>104200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7800</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>7300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>8000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>9500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2400</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1449,34 +1472,34 @@
         <v>51900</v>
       </c>
       <c r="E15" s="3">
+        <v>51900</v>
+      </c>
+      <c r="F15" s="3">
         <v>51700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>51200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>51400</v>
       </c>
       <c r="H15" s="3">
         <v>51400</v>
       </c>
       <c r="I15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="J15" s="3">
         <v>50800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>53900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>50500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>21000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7100</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>10</v>
@@ -1490,8 +1513,8 @@
       <c r="R15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1508,8 +1531,8 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>10</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>10</v>
@@ -1526,14 +1549,14 @@
       <c r="AD15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF15" s="3">
         <v>2500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2400</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>2300</v>
       </c>
       <c r="AH15" s="3">
         <v>2300</v>
@@ -1541,8 +1564,11 @@
       <c r="AI15" s="3">
         <v>2300</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1575,210 +1601,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>754500</v>
+        <v>675300</v>
       </c>
       <c r="E17" s="3">
-        <v>2469000</v>
+        <v>666700</v>
       </c>
       <c r="F17" s="3">
         <v>702500</v>
       </c>
       <c r="G17" s="3">
-        <v>717700</v>
+        <v>642400</v>
       </c>
       <c r="H17" s="3">
-        <v>692000</v>
+        <v>689000</v>
       </c>
       <c r="I17" s="3">
-        <v>746500</v>
+        <v>667300</v>
       </c>
       <c r="J17" s="3">
+        <v>716800</v>
+      </c>
+      <c r="K17" s="3">
         <v>780000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>727000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>557700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>381600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>260100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>227900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>153300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>151100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>192100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>178500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>118100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>123000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>117100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>105800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>103200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>116800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>105100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>101800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>105100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>122600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>111000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>53400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>49300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>54500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>46900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-117500</v>
+        <v>51800</v>
       </c>
       <c r="E18" s="3">
-        <v>-1758000</v>
+        <v>-29700</v>
       </c>
       <c r="F18" s="3">
-        <v>40100</v>
+        <v>8500</v>
       </c>
       <c r="G18" s="3">
-        <v>26300</v>
+        <v>100200</v>
       </c>
       <c r="H18" s="3">
-        <v>-26900</v>
+        <v>55000</v>
       </c>
       <c r="I18" s="3">
-        <v>99600</v>
+        <v>-2200</v>
       </c>
       <c r="J18" s="3">
+        <v>129300</v>
+      </c>
+      <c r="K18" s="3">
         <v>86500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>56800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>55700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>620700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>376800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>281800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>23300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>224200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>617100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>297600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>83700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>51700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>35100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>20700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>31200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>27600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>15600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>46500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>19200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>5900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1814,41 +1847,42 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3200</v>
+        <v>-6100</v>
       </c>
       <c r="E20" s="3">
-        <v>6200</v>
+        <v>-2700</v>
       </c>
       <c r="F20" s="3">
-        <v>-2300</v>
+        <v>-5300</v>
       </c>
       <c r="G20" s="3">
-        <v>5700</v>
+        <v>3700</v>
       </c>
       <c r="H20" s="3">
-        <v>8000</v>
+        <v>-4400</v>
       </c>
       <c r="I20" s="3">
-        <v>2600</v>
+        <v>-6200</v>
       </c>
       <c r="J20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-7300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3900</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1868,11 +1902,11 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1915,195 +1949,201 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1800</v>
+        <v>109800</v>
       </c>
       <c r="E21" s="3">
-        <v>-1636900</v>
+        <v>24900</v>
       </c>
       <c r="F21" s="3">
-        <v>153200</v>
+        <v>65500</v>
       </c>
       <c r="G21" s="3">
-        <v>145100</v>
+        <v>147700</v>
       </c>
       <c r="H21" s="3">
-        <v>95600</v>
+        <v>110800</v>
       </c>
       <c r="I21" s="3">
-        <v>216400</v>
+        <v>55400</v>
       </c>
       <c r="J21" s="3">
+        <v>181700</v>
+      </c>
+      <c r="K21" s="3">
         <v>195800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>164900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>97800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>637500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>391100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>294600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>37800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>236900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>629400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>310000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>94400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>64100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>50100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>33000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>43100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>39500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>26300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>58600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>16800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>24900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>11100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>48600</v>
+        <v>49500</v>
       </c>
       <c r="E22" s="3">
-        <v>47100</v>
+        <v>47800</v>
       </c>
       <c r="F22" s="3">
-        <v>47000</v>
+        <v>46300</v>
       </c>
       <c r="G22" s="3">
-        <v>47500</v>
+        <v>46200</v>
       </c>
       <c r="H22" s="3">
-        <v>45500</v>
+        <v>46600</v>
       </c>
       <c r="I22" s="3">
-        <v>42200</v>
+        <v>44700</v>
       </c>
       <c r="J22" s="3">
+        <v>41400</v>
+      </c>
+      <c r="K22" s="3">
         <v>38100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>29400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4600</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>4800</v>
       </c>
       <c r="AA22" s="3">
         <v>4800</v>
       </c>
       <c r="AB22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AC22" s="3">
         <v>6800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>7900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9200</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>2800</v>
       </c>
       <c r="AF22" s="3">
         <v>2800</v>
@@ -2112,215 +2152,224 @@
         <v>2800</v>
       </c>
       <c r="AH22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AI22" s="3">
         <v>3100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-162900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1798900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-64400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>60000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>41100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>31300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>42900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>620600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>375400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>281500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>221800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>615500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>295800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>80200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>48800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>32500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>17500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>26600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>22700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>38700</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-5300</v>
       </c>
       <c r="AE23" s="3">
         <v>-5300</v>
       </c>
       <c r="AF23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-13800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>16400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-15200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-92900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-16200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-11200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>23600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>140700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>84100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>65700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>43700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>145400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>63500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>12500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2420,210 +2469,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-147700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1706000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-53200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>48800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>30300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>479900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>291300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>215800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>178100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>470100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>232300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>67700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>40200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>30600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>16200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>24800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>32500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>10800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>34000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>14300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-147700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1706000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-53200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>48800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>30300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>479900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>291300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>215800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>178100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>470100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>232300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>67700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>40200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>16200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>24800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>32500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>10800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>34000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>14300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2723,8 +2781,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2824,8 +2885,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2925,8 +2989,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3026,41 +3093,44 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3200</v>
+        <v>6100</v>
       </c>
       <c r="E32" s="3">
-        <v>-6200</v>
+        <v>2700</v>
       </c>
       <c r="F32" s="3">
-        <v>2300</v>
+        <v>5300</v>
       </c>
       <c r="G32" s="3">
-        <v>-5700</v>
+        <v>-3700</v>
       </c>
       <c r="H32" s="3">
-        <v>-8000</v>
+        <v>4400</v>
       </c>
       <c r="I32" s="3">
-        <v>-2600</v>
+        <v>6200</v>
       </c>
       <c r="J32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K32" s="3">
         <v>7300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3900</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -3080,11 +3150,11 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -3127,109 +3197,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-147700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1706000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-53200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>48800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>30300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>479900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>291300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>215800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>178100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>470100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>232300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>67700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>40200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>30600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>16200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>24800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>32500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>10800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>34000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>14300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3329,215 +3405,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-147700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1706000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-53200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>48800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>30300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>479900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>291300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>215800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>178100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>470100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>232300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>67700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>40200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>30600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>16200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>24800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>32500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>10800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>34000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>14300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45200</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45109</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45018</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44927</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44836</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44745</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3573,8 +3658,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3610,147 +3696,151 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>143700</v>
+      </c>
+      <c r="E41" s="3">
         <v>107000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>78500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>118900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>149300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>178600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>353900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>292900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>212200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>379000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1275500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>802800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>578400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>593200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>981100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>489900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>77500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>72600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>108800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>52800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>28900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>28600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>56900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>43700</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>38700</v>
       </c>
       <c r="AB41" s="3">
         <v>38700</v>
       </c>
       <c r="AC41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="AD41" s="3">
         <v>101800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>36100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>173000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>175000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>197500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>169500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>48400</v>
+        <v>300</v>
       </c>
       <c r="G42" s="3">
-        <v>43900</v>
+        <v>48600</v>
       </c>
       <c r="H42" s="3">
+        <v>48800</v>
+      </c>
+      <c r="I42" s="3">
         <v>45100</v>
       </c>
-      <c r="I42" s="3">
-        <v>42800</v>
-      </c>
       <c r="J42" s="3">
+        <v>54600</v>
+      </c>
+      <c r="K42" s="3">
         <v>52100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>51800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>52500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>44300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>25800</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>10</v>
@@ -3767,8 +3857,8 @@
       <c r="T42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3812,450 +3902,465 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>541700</v>
+      </c>
+      <c r="E43" s="3">
         <v>497300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>476100</v>
       </c>
-      <c r="F43" s="3">
-        <v>454200</v>
-      </c>
       <c r="G43" s="3">
+        <v>488400</v>
+      </c>
+      <c r="H43" s="3">
         <v>520200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>426600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>454700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>542100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>557100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>514700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>590000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>393800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>350600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>85600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>105500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>529200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>376100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>120400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>110800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>104900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>86700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>57100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>81100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>76900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>91700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>44700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>92300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>67000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>41600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>19800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>20900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>25000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>577000</v>
+      </c>
+      <c r="E44" s="3">
         <v>602000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>583100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>577800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>551700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>542200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>528600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>524100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>536200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>552700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>181400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>198800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>197000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>218500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>174700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>113800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>95200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>92600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>58700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>58100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>61700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>64600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>66600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>67400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>63300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>59700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>58000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>67100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>23400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>23000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>22500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>26000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>135000</v>
+        <v>61500</v>
       </c>
       <c r="E45" s="3">
-        <v>74700</v>
+        <v>66500</v>
       </c>
       <c r="F45" s="3">
-        <v>111200</v>
+        <v>8400</v>
       </c>
       <c r="G45" s="3">
-        <v>106200</v>
+        <v>9800</v>
       </c>
       <c r="H45" s="3">
-        <v>115600</v>
+        <v>9100</v>
       </c>
       <c r="I45" s="3">
-        <v>118900</v>
+        <v>19700</v>
       </c>
       <c r="J45" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K45" s="3">
         <v>163900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>87900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>60200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>20300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>21500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>24900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>16000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>161000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1412600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1341300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1212400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1310500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1371300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1308100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1498900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1575100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1445200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1559100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2113700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1440300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1149100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>917700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1282700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1142400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>560900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>296900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>286500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>222200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>185400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>157500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>211600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>193400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>200100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>168000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>268000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>331200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>244500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>225300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>244900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>225400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>24600</v>
       </c>
       <c r="F47" s="3">
+        <v>23400</v>
+      </c>
+      <c r="G47" s="3">
         <v>7400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>24700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>33800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>21000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>15200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>37900</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>10</v>
@@ -4272,8 +4377,8 @@
       <c r="T47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -4317,70 +4422,73 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1539200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1503900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1621800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1613400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1541600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1553600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1541100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1520000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1425300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1279000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>489300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>476800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>452200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>385900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>307100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>211000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>189800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>172600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>170400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>171900</v>
-      </c>
-      <c r="W48" s="3">
-        <v>161300</v>
       </c>
       <c r="X48" s="3">
         <v>161300</v>
@@ -4389,138 +4497,144 @@
         <v>161300</v>
       </c>
       <c r="Z48" s="3">
+        <v>161300</v>
+      </c>
+      <c r="AA48" s="3">
         <v>73900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>70200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>66500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>62900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>61600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>50000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>51000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>49900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>50900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3566500</v>
+      </c>
+      <c r="E49" s="3">
         <v>3568500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3622100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5426300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5419400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5506600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5569800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5600600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5581600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5784500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>428600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>435700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>442700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>446600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>453200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>459500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>465300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>471500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>478300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>485100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>491500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>498200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>505100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>512100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>519000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>526000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>533000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>540900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>118800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>121500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>109100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>111500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4620,8 +4734,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4721,109 +4838,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>275500</v>
+        <v>257100</v>
       </c>
       <c r="E52" s="3">
-        <v>247000</v>
+        <v>226200</v>
       </c>
       <c r="F52" s="3">
-        <v>205500</v>
+        <v>198700</v>
       </c>
       <c r="G52" s="3">
-        <v>194900</v>
+        <v>179600</v>
       </c>
       <c r="H52" s="3">
-        <v>157300</v>
+        <v>179200</v>
       </c>
       <c r="I52" s="3">
-        <v>143500</v>
+        <v>141200</v>
       </c>
       <c r="J52" s="3">
+        <v>127000</v>
+      </c>
+      <c r="K52" s="3">
         <v>139100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>183100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>184600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>40800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>39700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>62400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>57500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>54400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>58300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>33300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>31900</v>
-      </c>
-      <c r="U52" s="3">
-        <v>31600</v>
       </c>
       <c r="V52" s="3">
         <v>31600</v>
       </c>
       <c r="W52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="X52" s="3">
         <v>29400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>29200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>27800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>27000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4923,109 +5046,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6801100</v>
+      </c>
+      <c r="E54" s="3">
         <v>6689200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6703300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8563100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8539100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8550300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8787100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8855800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8655500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8822400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3093100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2430400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2106400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1807700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2097400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1871200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1249400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>972900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>966800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>910900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>867500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>846200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>905900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>806400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>793900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>763500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>865600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>935300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>413800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>398500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>404500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>388300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>376500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5061,8 +5190,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5098,141 +5228,145 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>247200</v>
+      </c>
+      <c r="E57" s="3">
         <v>237400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>249600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>294800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>253000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>225900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>241500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>283300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>241800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>247300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>157500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>101500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>82700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>99600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>82100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>86300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>49400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>37500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>33200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>26700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>30400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>24800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>26800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>25200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>25700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>21700</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>27300</v>
       </c>
       <c r="AD57" s="3">
         <v>27300</v>
       </c>
       <c r="AE57" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AF57" s="3">
         <v>15700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>11200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>16000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>356400</v>
+        <v>405100</v>
       </c>
       <c r="E58" s="3">
-        <v>161100</v>
+        <v>385900</v>
       </c>
       <c r="F58" s="3">
-        <v>139800</v>
+        <v>189900</v>
       </c>
       <c r="G58" s="3">
-        <v>193000</v>
+        <v>166500</v>
       </c>
       <c r="H58" s="3">
-        <v>207400</v>
+        <v>219300</v>
       </c>
       <c r="I58" s="3">
+        <v>233700</v>
+      </c>
+      <c r="J58" s="3">
+        <v>233600</v>
+      </c>
+      <c r="K58" s="3">
         <v>207500</v>
       </c>
-      <c r="J58" s="3">
-        <v>207500</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>207600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>207800</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>10</v>
@@ -5246,47 +5380,47 @@
       <c r="Q58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>6700</v>
-      </c>
-      <c r="T58" s="3">
-        <v>12800</v>
       </c>
       <c r="U58" s="3">
         <v>12800</v>
       </c>
       <c r="V58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="W58" s="3">
         <v>13100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>21200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>12900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>55400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>54400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>53900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>53400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>94700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>20200</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>100</v>
       </c>
       <c r="AF58" s="3">
         <v>100</v>
@@ -5298,245 +5432,254 @@
         <v>100</v>
       </c>
       <c r="AI58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>338600</v>
+        <v>134800</v>
       </c>
       <c r="E59" s="3">
-        <v>369100</v>
+        <v>133000</v>
       </c>
       <c r="F59" s="3">
-        <v>399200</v>
+        <v>141400</v>
       </c>
       <c r="G59" s="3">
-        <v>414000</v>
+        <v>175700</v>
       </c>
       <c r="H59" s="3">
-        <v>356700</v>
+        <v>157500</v>
       </c>
       <c r="I59" s="3">
-        <v>458800</v>
+        <v>163600</v>
       </c>
       <c r="J59" s="3">
+        <v>250100</v>
+      </c>
+      <c r="K59" s="3">
         <v>516200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>423300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>444900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>335200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>222000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>214400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>109700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>284800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>250600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>151800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>132700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>90300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>86100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>75600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>74400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>77400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>80200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>78900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>77200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>75300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>80900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>23200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>20000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>18600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1027300</v>
+      </c>
+      <c r="E60" s="3">
         <v>932400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>779800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>833800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>860000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>790000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>907800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1007000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>872700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>900000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>492700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>323500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>297100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>209300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>366900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>337000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>207900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>183000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>136200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>125900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>127200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>112100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>159600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>159700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>158400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>152300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>197300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>128300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>38900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>31300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>29100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>33600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2207200</v>
+        <v>2374700</v>
       </c>
       <c r="E61" s="3">
-        <v>2241000</v>
+        <v>2384900</v>
       </c>
       <c r="F61" s="3">
-        <v>2274800</v>
+        <v>2422800</v>
       </c>
       <c r="G61" s="3">
-        <v>2274600</v>
+        <v>2454500</v>
       </c>
       <c r="H61" s="3">
-        <v>2308500</v>
+        <v>2450500</v>
       </c>
       <c r="I61" s="3">
-        <v>2379600</v>
+        <v>2489700</v>
       </c>
       <c r="J61" s="3">
+        <v>2588000</v>
+      </c>
+      <c r="K61" s="3">
         <v>2430800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2482000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2533300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5562,150 +5705,156 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>4400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>22800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>53200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>83200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>81000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>132200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>377300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>152400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>151000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>149700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>148300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>376100</v>
+        <v>77800</v>
       </c>
       <c r="E62" s="3">
-        <v>374800</v>
+        <v>54600</v>
       </c>
       <c r="F62" s="3">
-        <v>448600</v>
+        <v>53200</v>
       </c>
       <c r="G62" s="3">
-        <v>437800</v>
+        <v>62800</v>
       </c>
       <c r="H62" s="3">
-        <v>449300</v>
+        <v>51900</v>
       </c>
       <c r="I62" s="3">
-        <v>503200</v>
+        <v>55000</v>
       </c>
       <c r="J62" s="3">
+        <v>73300</v>
+      </c>
+      <c r="K62" s="3">
         <v>483400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>505500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>469500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>185500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>177500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>175200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>187300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>240700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>201500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>192200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>178200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>225400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>220800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>201700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>201300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>247700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>167900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>163800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>161300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>205500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>202500</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>3600</v>
       </c>
       <c r="AF62" s="3">
         <v>3600</v>
       </c>
       <c r="AG62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AH62" s="3">
         <v>5600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5805,8 +5954,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5906,8 +6058,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6007,109 +6162,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3614400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3515700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3395600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3557200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3572400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3547800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3790600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3921200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3860200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3902800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>678200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>501000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>472300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>396600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>607700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>538500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>400100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>361200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>361600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>351000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>333400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>336200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>445200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>380800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>405400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>394600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>535000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>708100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>194900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>185900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>184400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>187600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6145,8 +6306,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6246,8 +6408,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6347,8 +6512,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6448,8 +6616,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6549,109 +6720,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>314200</v>
+      </c>
+      <c r="E72" s="3">
         <v>334100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>481800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2187800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2180800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2193500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2246700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2197900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2167600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2148400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2129100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1649200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1357900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1142100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1123100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>945000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>474800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>242600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>174900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>134700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>104100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>87900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>86600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>61800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>29300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-7300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>10000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6751,8 +6928,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6852,8 +7032,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6953,109 +7136,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3186700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3173500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3307700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5005900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4966700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5002500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4996500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4934600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4795300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4919600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2414900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1929400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1634100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1411100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1489700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1332700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>849200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>611700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>605200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>559800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>534200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>510000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>460700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>425600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>388500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>368900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>330600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>227100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>218900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>212600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>220100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>200600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>196700</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7155,215 +7344,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45200</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45109</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45018</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44927</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44836</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44745</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-147700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1706000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-53200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>48800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>30300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>479900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>291300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>215800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>178100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>470100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>232300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>67700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>40200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>30600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>16200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>24800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>32500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>10800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>34000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>14300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7399,109 +7597,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>116100</v>
+        <v>61700</v>
       </c>
       <c r="E83" s="3">
-        <v>114900</v>
+        <v>63100</v>
       </c>
       <c r="F83" s="3">
-        <v>115400</v>
+        <v>63400</v>
       </c>
       <c r="G83" s="3">
-        <v>113100</v>
+        <v>62700</v>
       </c>
       <c r="H83" s="3">
-        <v>114500</v>
+        <v>53700</v>
       </c>
       <c r="I83" s="3">
-        <v>114200</v>
+        <v>26500</v>
       </c>
       <c r="J83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K83" s="3">
         <v>116600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>104200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>46000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>16800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>11900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>15100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>11500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>6200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5700</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>5200</v>
       </c>
       <c r="AI83" s="3">
         <v>5200</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7601,8 +7803,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7702,8 +7907,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7803,8 +8011,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7904,8 +8115,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8005,109 +8219,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>117900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-97900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>80400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>41500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>188900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>169400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>224600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>501000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>321400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>77100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-178000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>585500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>439100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>70500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>59000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>61200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>47700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>40500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>32900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>43200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>50600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>35800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>11200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>29600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>16600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8143,109 +8363,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-66100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-48600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-43400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-51300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-66000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-61700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-106900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-75200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-78300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-28800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-22700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4900</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-4700</v>
       </c>
       <c r="AE91" s="3">
         <v>-4700</v>
       </c>
       <c r="AF91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8345,8 +8569,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8446,109 +8673,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-20200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-55100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-42300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-68900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-59300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1530400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-24700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-96000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-93200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-65700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-64600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-27200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-22700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>141700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-404600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8584,31 +8817,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8685,8 +8919,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8786,8 +9023,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8887,8 +9127,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8988,186 +9231,192 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E100" s="3">
         <v>162500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-57800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-48700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-99700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-59600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-31700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-126000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>413100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-144300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-29600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-43200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-87700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-15500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-62100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-14700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-29600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-105200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-111800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>256500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>9900</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>2100</v>
       </c>
       <c r="AG100" s="3">
         <v>2100</v>
       </c>
       <c r="AH100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AI100" s="3">
         <v>3600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-800</v>
+        <v>-1200</v>
       </c>
       <c r="E101" s="3">
-        <v>-1100</v>
+        <v>-2700</v>
       </c>
       <c r="F101" s="3">
-        <v>2100</v>
+        <v>600</v>
       </c>
       <c r="G101" s="3">
-        <v>-1200</v>
+        <v>2300</v>
       </c>
       <c r="H101" s="3">
-        <v>-2700</v>
+        <v>-1900</v>
       </c>
       <c r="I101" s="3">
-        <v>600</v>
+        <v>-2300</v>
       </c>
       <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2300</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-100</v>
       </c>
       <c r="N101" s="3">
         <v>-100</v>
       </c>
       <c r="O101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
       <c r="Z101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA101" s="3">
         <v>200</v>
       </c>
       <c r="AB101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -9190,105 +9439,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E102" s="3">
         <v>28500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-40500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-29700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-175300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>61000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>80700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-167400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-895000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>472800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>224300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-387800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>491100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>412400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-36200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>56000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>23900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-28400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>13200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5000</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-63100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>65700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-136900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-22400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>28000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>16100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
   <si>
     <t>QDEL</t>
   </si>
@@ -656,465 +656,477 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E7" s="2">
         <v>45564</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45200</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45109</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45018</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44927</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44836</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44745</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>707800</v>
+      </c>
+      <c r="E8" s="3">
         <v>727100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>637000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>711000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>742600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>744000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>665100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>846100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>866500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>783800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>613400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1002300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>636900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>509700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>176600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>375300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>809200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>476100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>201800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>174700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>152200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>126500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>108300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>148000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>132600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>117400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>103200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>169100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>114900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>50900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>38300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>73700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>52800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>381700</v>
+      </c>
+      <c r="E9" s="3">
         <v>374800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>361000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>378900</v>
       </c>
-      <c r="G9" s="3">
-        <v>361300</v>
-      </c>
       <c r="H9" s="3">
+        <v>360000</v>
+      </c>
+      <c r="I9" s="3">
         <v>374600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>368600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>397500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>417500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>376300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>275900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>522600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>147500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>136300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>70400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>73400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>107700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>92400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>53000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>59700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>57300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>50600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>49100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>57000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>50500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>47800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>45500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>62900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>60900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>19400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>17800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>23600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>19100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>326100</v>
+      </c>
+      <c r="E10" s="3">
         <v>352300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>276000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>332100</v>
       </c>
-      <c r="G10" s="3">
-        <v>381300</v>
-      </c>
       <c r="H10" s="3">
+        <v>382600</v>
+      </c>
+      <c r="I10" s="3">
         <v>369400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>296500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>448600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>449000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>407500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>337500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>479700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>489400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>373400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>106200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>301900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>701500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>383700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>148800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>115000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>94900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>75900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>59200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>91000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>82100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>69600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>57700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>106200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>54000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>31500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>20500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>50100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>33700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1151,112 +1163,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E12" s="3">
         <v>55900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>56300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>59200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>59300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>61500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>62400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>62300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>64300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>65600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>34200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>22600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>23300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>25500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>21400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>21000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>16400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>14900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>11700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>13900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>12600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>13100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>13300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>12600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>10700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>7900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1359,150 +1375,156 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>147400</v>
+      </c>
+      <c r="E14" s="3">
         <v>36800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>87800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1766500</v>
       </c>
-      <c r="G14" s="3">
-        <v>60100</v>
-      </c>
       <c r="H14" s="3">
+        <v>61400</v>
+      </c>
+      <c r="I14" s="3">
         <v>28700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>24700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>29700</v>
-      </c>
-      <c r="K14" s="3">
-        <v>26400</v>
       </c>
       <c r="L14" s="3">
         <v>26400</v>
       </c>
       <c r="M14" s="3">
+        <v>26400</v>
+      </c>
+      <c r="N14" s="3">
         <v>104200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7800</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>7300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>8000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>9500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2400</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>51900</v>
+        <v>47900</v>
       </c>
       <c r="E15" s="3">
         <v>51900</v>
       </c>
       <c r="F15" s="3">
+        <v>51900</v>
+      </c>
+      <c r="G15" s="3">
         <v>51700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>51200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>51400</v>
       </c>
       <c r="I15" s="3">
         <v>51400</v>
       </c>
       <c r="J15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="K15" s="3">
         <v>50800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>53900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>50500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7100</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>10</v>
@@ -1516,8 +1538,8 @@
       <c r="S15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1534,8 +1556,8 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>10</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>10</v>
@@ -1552,14 +1574,14 @@
       <c r="AE15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG15" s="3">
         <v>2500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2400</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>2300</v>
       </c>
       <c r="AI15" s="3">
         <v>2300</v>
@@ -1567,8 +1589,11 @@
       <c r="AJ15" s="3">
         <v>2300</v>
       </c>
+      <c r="AK15" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1602,216 +1627,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>660800</v>
+      </c>
+      <c r="E17" s="3">
         <v>675300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>666700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>702500</v>
       </c>
-      <c r="G17" s="3">
-        <v>642400</v>
-      </c>
       <c r="H17" s="3">
+        <v>641100</v>
+      </c>
+      <c r="I17" s="3">
         <v>689000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>667300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>716800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>780000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>727000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>557700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>381600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>260100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>227900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>153300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>151100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>192100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>178500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>118100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>123000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>117100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>105800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>103200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>116800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>105100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>101800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>105100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>122600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>111000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>53400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>49300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>54500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>46900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E18" s="3">
         <v>51800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-29700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8500</v>
       </c>
-      <c r="G18" s="3">
-        <v>100200</v>
-      </c>
       <c r="H18" s="3">
+        <v>101500</v>
+      </c>
+      <c r="I18" s="3">
         <v>55000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>129300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>86500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>56800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>55700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>620700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>376800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>281800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>23300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>224200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>617100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>297600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>83700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>51700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>35100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>31200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>27600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>15600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>46500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>19200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1848,44 +1880,45 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3900</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1905,11 +1938,11 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1952,201 +1985,207 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>99100</v>
+      </c>
+      <c r="E21" s="3">
         <v>109800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>24900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>65500</v>
       </c>
-      <c r="G21" s="3">
-        <v>147700</v>
-      </c>
       <c r="H21" s="3">
+        <v>149000</v>
+      </c>
+      <c r="I21" s="3">
         <v>110800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>55400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>181700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>195800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>164900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>97800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>637500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>391100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>294600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>37800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>236900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>629400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>310000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>94400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>64100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>50100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>33000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>43100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>39500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>26300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>58600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>16800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>24900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E22" s="3">
         <v>49500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>47800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>46300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>46200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>46600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>44700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>41400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>38100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>29400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4600</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>4800</v>
       </c>
       <c r="AB22" s="3">
         <v>4800</v>
       </c>
       <c r="AC22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AD22" s="3">
         <v>6800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9200</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>2800</v>
       </c>
       <c r="AG22" s="3">
         <v>2800</v>
@@ -2155,221 +2194,230 @@
         <v>2800</v>
       </c>
       <c r="AI22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-140900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-28800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-162900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1798900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-64400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>60000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>41100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>42900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>620600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>375400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>281500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>21700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>221800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>615500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>295800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>80200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>48800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>32500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>26600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>22700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>10800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-8800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>38700</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-5300</v>
       </c>
       <c r="AF23" s="3">
         <v>-5300</v>
       </c>
       <c r="AG23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-13800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>16400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-8900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-15200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-92900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-16200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-11200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>23600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>140700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>84100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>65700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>43700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>145400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>63500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2472,216 +2520,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-178400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-147700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1706000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-53200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>48800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>30300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>479900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>291300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>215800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>178100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>470100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>232300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>67700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>40200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>30600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>16200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>24800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>32500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>10800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>34000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>14300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-178400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-147700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1706000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-53200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>48800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>30300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>479900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>291300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>215800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>178100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>470100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>232300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>67700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>40200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>30600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>16200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>24800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>32500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>10800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>34000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>14300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2784,8 +2841,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2888,8 +2948,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2992,8 +3055,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3096,44 +3162,47 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E32" s="3">
         <v>6100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3900</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3153,11 +3222,11 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3200,112 +3269,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-178400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-147700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1706000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-53200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>48800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>30300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>479900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>291300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>215800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>178100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>470100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>232300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>67700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>40200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>30600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>16200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>24800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>32500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>10800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>34000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>14300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3408,221 +3483,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-178400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-147700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1706000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-53200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>48800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>30300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>479900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>291300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>215800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>178100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>470100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>232300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>67700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>40200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>30600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>16200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>24800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>32500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>10800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>34000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>14300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E38" s="2">
         <v>45564</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45200</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45109</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45018</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44927</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44836</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44745</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3659,8 +3743,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3697,153 +3782,157 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>98300</v>
+      </c>
+      <c r="E41" s="3">
         <v>143700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>107000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>118900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>149300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>178600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>353900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>292900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>212200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>379000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1275500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>802800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>578400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>593200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>981100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>489900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>77500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>72600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>108800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>52800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>28900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>28600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>56900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>43700</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>38700</v>
       </c>
       <c r="AC41" s="3">
         <v>38700</v>
       </c>
       <c r="AD41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="AE41" s="3">
         <v>101800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>36100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>173000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>175000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>197500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>169500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E42" s="3">
         <v>2300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>48600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>48800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>45100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>54600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>52100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>51800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>52500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>44300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>25800</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>10</v>
@@ -3860,8 +3949,8 @@
       <c r="U42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3905,465 +3994,480 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>451300</v>
+      </c>
+      <c r="E43" s="3">
         <v>541700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>497300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>476100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>488400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>520200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>426600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>454700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>542100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>557100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>514700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>590000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>393800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>350600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>85600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>105500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>529200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>376100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>120400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>110800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>104900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>86700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>57100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>81100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>76900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>91700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>44700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>92300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>67000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>41600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>19800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>20900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>25000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>533700</v>
+      </c>
+      <c r="E44" s="3">
         <v>577000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>602000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>583100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>577800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>551700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>542200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>528600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>524100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>536200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>552700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>181400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>198800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>197000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>218500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>174700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>113800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>95200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>92600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>58700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>58100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>61700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>64600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>66600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>67400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>63300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>59700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>58000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>67100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>23400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>23000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>22500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E45" s="3">
         <v>61500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>66500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>19700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>163900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>87900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>60200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>22500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>20300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>21500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>24900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>16000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>161000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1218900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1412600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1341300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1212400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1310500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1371300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1308100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1498900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1575100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1445200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1559100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2113700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1440300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1149100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>917700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1282700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1142400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>560900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>296900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>286500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>222200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>185400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>157500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>211600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>193400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>200100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>168000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>268000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>331200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>244500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>225300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>244900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>225400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3">
         <v>24600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>23400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>24700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>33800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>21000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>15200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>37900</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>10</v>
@@ -4380,8 +4484,8 @@
       <c r="U47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4425,73 +4529,76 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1548900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1539200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1503900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1621800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1613400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1541600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1553600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1541100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1520000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1425300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1279000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>489300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>476800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>452200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>385900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>307100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>211000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>189800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>172600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>170400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>171900</v>
-      </c>
-      <c r="X48" s="3">
-        <v>161300</v>
       </c>
       <c r="Y48" s="3">
         <v>161300</v>
@@ -4500,141 +4607,147 @@
         <v>161300</v>
       </c>
       <c r="AA48" s="3">
+        <v>161300</v>
+      </c>
+      <c r="AB48" s="3">
         <v>73900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>70200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>66500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>62900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>61600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>50000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>51000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>49900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>50900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3385100</v>
+      </c>
+      <c r="E49" s="3">
         <v>3566500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3568500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3622100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5426300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5419400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5506600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5569800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5600600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5581600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5784500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>428600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>435700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>442700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>446600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>453200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>459500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>465300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>471500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>478300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>485100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>491500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>498200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>505100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>512100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>519000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>526000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>533000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>540900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>118800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>121500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>109100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>111500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4737,8 +4850,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4841,112 +4957,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>270700</v>
+      </c>
+      <c r="E52" s="3">
         <v>257100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>226200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>198700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>179600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>179200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>141200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>127000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>139100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>183100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>184600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>40800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>39700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>62400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>57500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>54400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>58300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>33300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>31900</v>
-      </c>
-      <c r="V52" s="3">
-        <v>31600</v>
       </c>
       <c r="W52" s="3">
         <v>31600</v>
       </c>
       <c r="X52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="Y52" s="3">
         <v>29400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>29200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>27800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>27000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5049,112 +5171,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6423600</v>
+      </c>
+      <c r="E54" s="3">
         <v>6801100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6689200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6703300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8563100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8539100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8550300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8787100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8855800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8655500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8822400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3093100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2430400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2106400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1807700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2097400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1871200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1249400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>972900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>966800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>910900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>867500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>846200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>905900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>806400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>793900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>763500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>865600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>935300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>413800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>398500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>404500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>388300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>376500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5191,8 +5319,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5229,147 +5358,151 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E57" s="3">
         <v>247200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>237400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>249600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>294800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>253000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>225900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>241500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>283300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>241800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>247300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>157500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>101500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>82700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>99600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>82100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>86300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>49400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>37500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>33200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>26700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>30400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>24800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>26800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>25200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>25700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>21700</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>27300</v>
       </c>
       <c r="AE57" s="3">
         <v>27300</v>
       </c>
       <c r="AF57" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AG57" s="3">
         <v>15700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>11200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>372900</v>
+      </c>
+      <c r="E58" s="3">
         <v>405100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>385900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>189900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>166500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>219300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>233700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>233600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>207500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>207600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>207800</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>10</v>
@@ -5383,47 +5516,47 @@
       <c r="R58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>6700</v>
-      </c>
-      <c r="U58" s="3">
-        <v>12800</v>
       </c>
       <c r="V58" s="3">
         <v>12800</v>
       </c>
       <c r="W58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="X58" s="3">
         <v>13100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>21200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>12900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>55400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>54400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>53900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>53400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>94700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>20200</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>100</v>
       </c>
       <c r="AG58" s="3">
         <v>100</v>
@@ -5435,254 +5568,263 @@
         <v>100</v>
       </c>
       <c r="AJ58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK58" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>135700</v>
+      </c>
+      <c r="E59" s="3">
         <v>134800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>133000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>141400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>175700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>157500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>163600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>250100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>516200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>423300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>444900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>335200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>222000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>214400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>109700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>284800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>250600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>151800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>132700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>90300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>86100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>75600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>74400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>77400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>80200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>78900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>77200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>75300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>80900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>23200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>20000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>18600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>17500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>998800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1027300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>932400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>779800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>833800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>860000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>790000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>907800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1007000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>872700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>900000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>492700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>323500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>297100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>209300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>366900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>337000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>207900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>183000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>136200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>125900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>127200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>112100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>159600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>159700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>158400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>152300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>197300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>128300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>38900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>31300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>29100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>33600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2308500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2374700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2384900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2422800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2454500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2450500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2489700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2588000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2430800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2482000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2533300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -5708,153 +5850,159 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>4400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>22800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>37900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>53200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>83200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>81000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>132200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>377300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>152400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>151000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>149700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>148300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E62" s="3">
         <v>77800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>54600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>53200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>62800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>51900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>55000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>73300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>483400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>505500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>469500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>185500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>177500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>175200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>187300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>240700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>201500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>192200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>178200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>225400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>220800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>201700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>201300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>247700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>167900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>163800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>161300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>205500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>202500</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>3600</v>
       </c>
       <c r="AG62" s="3">
         <v>3600</v>
       </c>
       <c r="AH62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AI62" s="3">
         <v>5600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5957,8 +6105,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6061,8 +6212,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6165,112 +6319,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3439100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3614400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3515700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3395600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3557200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3572400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3547800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3790600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3921200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3860200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3902800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>678200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>501000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>472300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>396600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>607700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>538500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>400100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>361200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>361600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>351000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>333400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>336200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>445200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>380800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>405400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>394600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>535000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>708100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>194900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>185900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>184400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>187600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6307,8 +6467,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6411,8 +6572,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6515,8 +6679,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6619,8 +6786,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6723,112 +6893,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>135800</v>
+      </c>
+      <c r="E72" s="3">
         <v>314200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>334100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>481800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2187800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2180800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2193500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2246700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2197900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2167600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2148400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2129100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1649200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1357900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1142100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1123100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>945000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>474800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>242600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>174900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>134700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>104100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>87900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>86600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>61800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>29300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>18500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>21500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-7300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>10000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6931,8 +7107,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7035,8 +7214,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7139,112 +7321,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2984500</v>
+      </c>
+      <c r="E76" s="3">
         <v>3186700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3173500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3307700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5005900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4966700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5002500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4996500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4934600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4795300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4919600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2414900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1929400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1634100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1411100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1489700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1332700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>849200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>611700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>605200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>559800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>534200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>510000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>460700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>425600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>388500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>368900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>330600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>227100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>218900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>212600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>220100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>200600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>196700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7347,221 +7535,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E80" s="2">
         <v>45564</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45200</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45109</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45018</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44927</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44836</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44745</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-178400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-147700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1706000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-53200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>48800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>30300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>479900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>291300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>215800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>178100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>470100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>232300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>67700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>40200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>30600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>16200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>24800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>32500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>10800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>34000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>14300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7598,112 +7795,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E83" s="3">
         <v>61700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>63100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>63400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>62700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>53700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>116600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>104200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>46000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>16800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>11900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>15100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>11500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>6200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5700</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>5200</v>
       </c>
       <c r="AJ83" s="3">
         <v>5200</v>
       </c>
+      <c r="AK83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7806,8 +8007,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7910,8 +8114,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8014,8 +8221,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8118,8 +8328,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8222,112 +8435,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E89" s="3">
         <v>117900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-97900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>80400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>41500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>188900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>169400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>224600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>501000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>321400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>77100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-178000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>585500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>439100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>70500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>59000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>61200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>47700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>13300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>40500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>32900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>43200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>50600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>35800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>11200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>29600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>16600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8364,112 +8583,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-35300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-66100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-48600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-43400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-51300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-66000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-61700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-30500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-22400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-106900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-75200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-78300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-28800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-22700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4900</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-4700</v>
       </c>
       <c r="AF91" s="3">
         <v>-4700</v>
       </c>
       <c r="AG91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8572,8 +8795,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8676,112 +8902,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-37900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-56500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-20200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-55100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-42300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-68900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-59300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1530400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-24700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-96000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-93200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-65700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-64600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-27200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>141700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-404600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8818,8 +9050,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8844,8 +9077,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8922,8 +9155,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9026,8 +9262,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9130,8 +9369,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9234,192 +9476,198 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-26300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>162500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-57800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-48700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-99700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-59600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-31700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-126000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>413100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-144300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-29600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-43200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-87700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-15500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-62100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-14700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-29600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-105200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-111800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>256500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>9900</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>2100</v>
       </c>
       <c r="AH100" s="3">
         <v>2100</v>
       </c>
       <c r="AI100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2300</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-100</v>
       </c>
       <c r="O101" s="3">
         <v>-100</v>
       </c>
       <c r="P101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
       <c r="AA101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB101" s="3">
         <v>200</v>
       </c>
       <c r="AC101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -9442,108 +9690,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-45500</v>
+      </c>
+      <c r="E102" s="3">
         <v>36500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>28500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-40500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-29700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-175300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>61000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>80700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-167400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-895000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>472800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>224300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-387800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>491100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>412400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-36200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>56000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>23900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-28400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5000</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>-63100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>65700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-136900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-22400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>28000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>16100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>QDEL</t>
   </si>
@@ -656,477 +656,490 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E7" s="2">
         <v>45655</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45564</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45200</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45109</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45018</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44927</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44836</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44745</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>692800</v>
+      </c>
+      <c r="E8" s="3">
         <v>707800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>727100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>637000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>711000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>742600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>744000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>665100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>846100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>866500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>783800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>613400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1002300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>636900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>509700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>176600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>375300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>809200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>476100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>201800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>174700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>152200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>126500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>108300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>148000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>132600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>117400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>103200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>169100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>114900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>50900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>38300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>73700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>52800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>349500</v>
+      </c>
+      <c r="E9" s="3">
         <v>381700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>374800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>361000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>378900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>360000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>374600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>368600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>397500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>417500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>376300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>275900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>522600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>147500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>136300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>70400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>73400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>107700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>92400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>53000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>59700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>57300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>50600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>49100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>57000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>50500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>47800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>45500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>62900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>60900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>19400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>17800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>23600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>19100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>343300</v>
+      </c>
+      <c r="E10" s="3">
         <v>326100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>352300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>276000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>332100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>382600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>369400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>296500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>448600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>449000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>407500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>337500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>479700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>489400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>373400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>106200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>301900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>701500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>383700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>148800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>115000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>94900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>75900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>59200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>91000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>82100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>69600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>57700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>106200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>54000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>31500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>20500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>50100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>33700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1164,115 +1177,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E12" s="3">
         <v>47300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>55900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>56300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>59200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>59300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>61500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>62400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>62300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>64300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>65600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>34200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>26100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>23700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>22600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>23300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>25500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>21400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>21000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>16400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>14900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>11700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>13900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>13100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>13300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>12600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>10700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>7600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>7500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1378,156 +1395,162 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E14" s="3">
         <v>147400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>36800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>87800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1766500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>61400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>28700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>24700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>29700</v>
-      </c>
-      <c r="L14" s="3">
-        <v>26400</v>
       </c>
       <c r="M14" s="3">
         <v>26400</v>
       </c>
       <c r="N14" s="3">
+        <v>26400</v>
+      </c>
+      <c r="O14" s="3">
         <v>104200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>10800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>4500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>7300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>8000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>9500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>4600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2400</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E15" s="3">
         <v>47900</v>
-      </c>
-      <c r="E15" s="3">
-        <v>51900</v>
       </c>
       <c r="F15" s="3">
         <v>51900</v>
       </c>
       <c r="G15" s="3">
+        <v>51900</v>
+      </c>
+      <c r="H15" s="3">
         <v>51700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>51200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>51400</v>
       </c>
       <c r="J15" s="3">
         <v>51400</v>
       </c>
       <c r="K15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="L15" s="3">
         <v>50800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>53900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>50500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>21000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7100</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>10</v>
@@ -1541,8 +1564,8 @@
       <c r="T15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1559,8 +1582,8 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>10</v>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>10</v>
@@ -1577,14 +1600,14 @@
       <c r="AF15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH15" s="3">
         <v>2500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>2400</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>2300</v>
       </c>
       <c r="AJ15" s="3">
         <v>2300</v>
@@ -1592,8 +1615,11 @@
       <c r="AK15" s="3">
         <v>2300</v>
       </c>
+      <c r="AL15" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1628,222 +1654,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>644100</v>
+      </c>
+      <c r="E17" s="3">
         <v>660800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>675300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>666700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>702500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>641100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>689000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>667300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>716800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>780000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>727000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>557700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>381600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>260100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>227900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>153300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>151100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>192100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>178500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>118100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>123000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>117100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>105800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>103200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>116800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>105100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>101800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>105100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>122600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>111000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>53400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>49300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>54500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>46900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E18" s="3">
         <v>47000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>51800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-29700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>101500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>55000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>129300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>86500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>56800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>55700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>620700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>376800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>281800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>23300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>224200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>617100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>297600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>83700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>51700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>35100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>20700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>31200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>27600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>15600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>46500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>19200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>5900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1881,47 +1914,48 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3900</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1941,11 +1975,11 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1988,207 +2022,213 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E21" s="3">
         <v>99100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>109800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>24900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>65500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>149000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>110800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>55400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>181700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>195800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>164900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>97800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>637500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>391100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>294600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>37800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>236900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>629400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>310000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>94400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>64100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>50100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>33000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>17600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>43100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>39500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>26300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>58600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>16800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>24900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>11100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E22" s="3">
         <v>44700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>49500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>47800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>46300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>46200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>46600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>44700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>41400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>38100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>29400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4600</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>4800</v>
       </c>
       <c r="AC22" s="3">
         <v>4800</v>
       </c>
       <c r="AD22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE22" s="3">
         <v>6800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>7900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9200</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>2800</v>
       </c>
       <c r="AH22" s="3">
         <v>2800</v>
@@ -2197,227 +2237,236 @@
         <v>2800</v>
       </c>
       <c r="AJ22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AK22" s="3">
         <v>3100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-140900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-28800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-162900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1798900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-64400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>60000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>41100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>42900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>620600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>375400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>281500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>21700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>221800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>615500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>295800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>80200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>48800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>32500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>17500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>26600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>22700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-8800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>38700</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>-5300</v>
       </c>
       <c r="AG23" s="3">
         <v>-5300</v>
       </c>
       <c r="AH23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-13800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>16400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E24" s="3">
         <v>37500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-8900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-15200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-92900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-16200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-11200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>23600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>140700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>84100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>65700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>43700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>145400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>63500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>12500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>4700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2523,222 +2572,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-178400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-147700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1706000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-53200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>48800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>30300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>479900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>291300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>215800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>178100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>470100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>232300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>67700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>40200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>30600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>16200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>24800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>32500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>10800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>34000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-178400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-147700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1706000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-53200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>48800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>30300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>479900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>291300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>215800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>178100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>470100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>232300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>67700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>40200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>30600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>16200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>24800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>32500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>10800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>34000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2844,8 +2902,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2951,8 +3012,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3058,8 +3122,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3165,47 +3232,50 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>4200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3900</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -3225,11 +3295,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>1100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -3272,115 +3342,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-178400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-147700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1706000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-53200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>48800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>30300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>479900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>291300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>215800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>178100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>470100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>232300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>67700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>40200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>30600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>16200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>24800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>32500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>34000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3486,227 +3562,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-178400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-147700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1706000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-53200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>48800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>30300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>479900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>291300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>215800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>178100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>470100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>232300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>67700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>40200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>30600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>16200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>24800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>32500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>34000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E38" s="2">
         <v>45655</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45564</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45200</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45109</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45018</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44927</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44836</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44745</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3744,8 +3829,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3783,159 +3869,163 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>127100</v>
+      </c>
+      <c r="E41" s="3">
         <v>98300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>143700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>107000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>78500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>118900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>149300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>178600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>353900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>292900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>212200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>379000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1275500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>802800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>578400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>593200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>981100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>489900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>77500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>72600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>108800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>52800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>28900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>28600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>56900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>43700</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>38700</v>
       </c>
       <c r="AD41" s="3">
         <v>38700</v>
       </c>
       <c r="AE41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="AF41" s="3">
         <v>101800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>36100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>173000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>175000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>197500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>169500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>900</v>
+      </c>
+      <c r="E42" s="3">
         <v>1300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>48600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>48800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>45100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>54600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>52100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>51800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>52500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>44300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>25800</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>10</v>
@@ -3952,8 +4042,8 @@
       <c r="V42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3997,436 +4087,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>437000</v>
+      </c>
+      <c r="E43" s="3">
         <v>451300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>541700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>497300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>476100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>488400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>520200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>426600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>454700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>542100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>557100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>514700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>590000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>393800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>350600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>85600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>105500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>529200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>376100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>120400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>110800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>104900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>86700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>57100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>81100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>76900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>91700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>44700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>92300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>67000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>41600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>19800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>25000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>563200</v>
+      </c>
+      <c r="E44" s="3">
         <v>533700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>577000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>602000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>583100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>577800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>551700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>542200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>528600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>524100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>536200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>552700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>181400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>198800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>197000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>218500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>174700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>113800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>95200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>92600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>58700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>58100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>61700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>64600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>66600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>67400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>63300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>59700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>58000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>67100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>23400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>23000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>22500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>26000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E45" s="3">
         <v>57000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>61500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>66500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>19700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>163900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>87900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>60200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>20300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>21500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>24900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>16000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>161000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>6500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1258200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1218900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1412600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1341300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1212400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1310500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1371300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1308100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1498900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1575100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1445200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1559100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2113700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1440300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1149100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>917700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1282700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1142400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>560900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>296900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>286500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>222200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>185400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>157500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>211600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>193400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>200100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>168000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>268000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>331200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>244500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>225300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>244900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>225400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4436,41 +4541,41 @@
       <c r="E47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3">
         <v>24600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>23400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>24700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>33800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>21000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>15200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>37900</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>10</v>
@@ -4487,8 +4592,8 @@
       <c r="V47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -4532,76 +4637,79 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1564400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1548900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1539200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1503900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1621800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1613400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1541600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1553600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1541100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1520000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1425300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1279000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>489300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>476800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>452200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>385900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>307100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>211000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>189800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>172600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>170400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>171900</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>161300</v>
       </c>
       <c r="Z48" s="3">
         <v>161300</v>
@@ -4610,144 +4718,150 @@
         <v>161300</v>
       </c>
       <c r="AB48" s="3">
+        <v>161300</v>
+      </c>
+      <c r="AC48" s="3">
         <v>73900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>70200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>66500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>62900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>61600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>50000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>51000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>49900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>50900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3368800</v>
+      </c>
+      <c r="E49" s="3">
         <v>3385100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3566500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3568500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3622100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5426300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5419400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5506600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5569800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5600600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5581600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5784500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>428600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>435700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>442700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>446600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>453200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>459500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>465300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>471500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>478300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>485100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>491500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>498200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>505100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>512100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>519000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>526000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>533000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>540900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>118800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>121500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>111500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4853,8 +4967,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4960,115 +5077,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>270200</v>
+      </c>
+      <c r="E52" s="3">
         <v>270700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>257100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>226200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>198700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>179600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>179200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>141200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>127000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>139100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>183100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>184600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>40800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>39700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>62400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>57500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>54400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>58300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>33300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>31900</v>
-      </c>
-      <c r="W52" s="3">
-        <v>31600</v>
       </c>
       <c r="X52" s="3">
         <v>31600</v>
       </c>
       <c r="Y52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="Z52" s="3">
         <v>29400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>29200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>27800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>27000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5174,115 +5297,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6461600</v>
+      </c>
+      <c r="E54" s="3">
         <v>6423600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6801100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6689200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6703300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8563100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8539100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8550300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8787100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8855800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8655500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8822400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3093100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2430400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2106400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1807700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2097400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1871200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1249400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>972900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>966800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>910900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>867500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>846200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>905900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>806400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>793900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>763500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>865600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>935300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>413800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>398500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>404500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>388300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>376500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5320,8 +5449,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5359,153 +5489,157 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>230900</v>
+      </c>
+      <c r="E57" s="3">
         <v>246000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>247200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>237400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>249600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>294800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>253000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>225900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>241500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>283300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>241800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>247300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>157500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>101500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>82700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>99600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>82100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>86300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>49400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>37500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>33200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>26700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>30400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>24800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>26800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>25200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>25700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>21700</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>27300</v>
       </c>
       <c r="AF57" s="3">
         <v>27300</v>
       </c>
       <c r="AG57" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AH57" s="3">
         <v>15700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>11200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>16000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>425000</v>
+      </c>
+      <c r="E58" s="3">
         <v>372900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>405100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>385900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>189900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>166500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>219300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>233700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>233600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>207500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>207600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>207800</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>10</v>
@@ -5519,47 +5653,47 @@
       <c r="S58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>6700</v>
-      </c>
-      <c r="V58" s="3">
-        <v>12800</v>
       </c>
       <c r="W58" s="3">
         <v>12800</v>
       </c>
       <c r="X58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="Y58" s="3">
         <v>13100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>21200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>12900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>55400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>54400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>53900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>53400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>94700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>20200</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>100</v>
       </c>
       <c r="AH58" s="3">
         <v>100</v>
@@ -5571,263 +5705,272 @@
         <v>100</v>
       </c>
       <c r="AK58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL58" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>125700</v>
+      </c>
+      <c r="E59" s="3">
         <v>135700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>134800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>133000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>141400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>175700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>157500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>163600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>250100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>516200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>423300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>444900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>335200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>222000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>214400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>109700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>284800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>250600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>151800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>132700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>90300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>86100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>75600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>74400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>77400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>80200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>78900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>77200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>75300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>80900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>23200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>20000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>18600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>17500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1047200</v>
+      </c>
+      <c r="E60" s="3">
         <v>998800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1027300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>932400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>779800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>833800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>860000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>790000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>907800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1007000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>872700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>900000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>492700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>323500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>297100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>209300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>366900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>337000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>207900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>183000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>136200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>125900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>127200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>112100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>159600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>159700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>158400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>152300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>197300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>128300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>38900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>31300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>29100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>33600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2272900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2308500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2374700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2384900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2422800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2454500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2450500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2489700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2588000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2430800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2482000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2533300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5853,156 +5996,162 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>4400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>22800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>37900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>53200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>83200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>81000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>132200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>377300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>152400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>151000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>149700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>148300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E62" s="3">
         <v>38000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>77800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>54600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>53200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>62800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>51900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>55000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>73300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>483400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>505500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>469500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>185500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>177500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>175200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>187300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>240700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>201500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>192200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>178200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>225400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>220800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>201700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>201300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>247700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>167900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>163800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>161300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>205500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>202500</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>3600</v>
       </c>
       <c r="AH62" s="3">
         <v>3600</v>
       </c>
       <c r="AI62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6108,8 +6257,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6215,8 +6367,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6322,115 +6477,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3464400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3439100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3614400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3515700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3395600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3557200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3572400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3547800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3790600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3921200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3860200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3902800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>678200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>501000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>472300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>396600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>607700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>538500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>400100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>361200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>361600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>351000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>333400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>336200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>445200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>380800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>405400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>394600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>535000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>708100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>194900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>185900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>184400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>187600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6468,8 +6629,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6575,8 +6737,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6682,8 +6847,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6789,8 +6957,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6896,115 +7067,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E72" s="3">
         <v>135800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>314200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>334100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>481800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2187800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2180800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2193500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2246700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2197900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2167600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2148400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2129100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1649200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1357900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1142100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1123100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>945000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>474800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>242600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>174900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>134700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>104100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>87900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>86600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>61800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>29300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>18500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-7300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7110,8 +7287,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7217,8 +7397,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7324,115 +7507,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2997200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2984500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3186700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3173500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3307700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5005900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4966700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5002500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4996500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4934600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4795300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4919600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2414900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1929400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1634100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1411100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1489700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1332700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>849200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>611700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>605200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>559800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>534200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>510000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>460700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>425600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>388500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>368900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>330600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>227100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>218900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>212600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>220100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>200600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>196700</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7538,227 +7727,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E80" s="2">
         <v>45655</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45564</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45200</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45109</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45018</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44927</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44836</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44745</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-178400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-147700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1706000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-53200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>48800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>30300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>479900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>291300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>215800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>178100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>470100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>232300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>67700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>40200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>30600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>16200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>24800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>32500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>34000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7796,115 +7994,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E83" s="3">
         <v>64200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>61700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>63100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>62700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>53700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>116600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>104200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>46000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>16800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>11900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>15100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>11900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>10700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>11500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>12900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>6200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5700</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>5200</v>
       </c>
       <c r="AK83" s="3">
         <v>5200</v>
       </c>
+      <c r="AL83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8010,8 +8212,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8117,8 +8322,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8224,8 +8432,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8331,8 +8542,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8438,115 +8652,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E89" s="3">
         <v>63700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>117900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-97900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>80400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>41500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>188900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>169400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>224600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>501000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>321400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>77100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-178000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>585500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>439100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>70500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>59000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>61200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>47700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>13300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>40500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>32900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>43200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>50600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>35800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>11200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>29600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>16600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8584,115 +8804,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-56200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-47200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-35300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-66100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-48600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-43400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-51300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-66000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-61700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-30500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-106900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-75200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-78300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-28800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-22700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4900</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-4700</v>
       </c>
       <c r="AG91" s="3">
         <v>-4700</v>
       </c>
       <c r="AH91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8798,8 +9022,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8905,115 +9132,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-56200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-37900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-56500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-20200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-55100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-42300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-68900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-59300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-29800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1530400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-24700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-96000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-93200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-65700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-64600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-27200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>141700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-404600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9051,8 +9284,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9080,8 +9314,8 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9158,8 +9392,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9265,8 +9502,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9372,8 +9612,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9479,198 +9722,204 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-68900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-26300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>162500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-57800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-48700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-99700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-59600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-31700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-126000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>413100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-144300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-29600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-43200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-87700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-15500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-62100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-14700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-29600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-105200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-111800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>256500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>9900</v>
-      </c>
-      <c r="AH100" s="3">
-        <v>2100</v>
       </c>
       <c r="AI100" s="3">
         <v>2100</v>
       </c>
       <c r="AJ100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AK100" s="3">
         <v>3600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>2100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2300</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-100</v>
       </c>
       <c r="P101" s="3">
         <v>-100</v>
       </c>
       <c r="Q101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
       <c r="AB101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AC101" s="3">
         <v>200</v>
       </c>
       <c r="AD101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AE101" s="3">
         <v>0</v>
@@ -9693,111 +9942,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-45500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>36500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>28500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-40500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-30400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-29700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-175300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>61000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>80700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-167400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-895000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>472800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>224300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-14800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-387800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>491100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>412400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-36200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>56000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>23900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-28400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5000</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-63100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>65700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-136900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>16100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>QDEL</t>
   </si>
@@ -656,490 +656,503 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E7" s="2">
         <v>45746</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45655</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45564</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45200</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45109</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45018</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44927</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44836</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44745</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>613900</v>
+      </c>
+      <c r="E8" s="3">
         <v>692800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>707800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>727100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>637000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>711000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>742600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>744000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>665100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>846100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>866500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>783800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>613400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1002300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>636900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>509700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>176600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>375300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>809200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>476100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>201800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>174700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>152200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>126500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>108300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>148000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>132600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>117400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>103200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>169100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>114900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>50900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>38300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>73700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>52800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>339000</v>
+      </c>
+      <c r="E9" s="3">
         <v>349500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>381700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>374800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>361000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>378900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>360000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>374600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>368600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>397500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>417500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>376300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>275900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>522600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>147500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>136300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>70400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>73400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>107700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>92400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>53000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>59700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>57300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>50600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>49100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>57000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>50500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>47800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>45500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>62900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>60900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>19400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>23600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>19100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>274900</v>
+      </c>
+      <c r="E10" s="3">
         <v>343300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>326100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>352300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>276000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>332100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>382600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>369400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>296500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>448600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>449000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>407500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>337500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>479700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>489400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>373400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>106200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>301900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>701500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>383700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>148800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>115000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>94900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>75900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>59200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>91000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>82100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>69600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>57700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>106200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>54000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>31500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>20500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>50100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>33700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1178,118 +1191,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E12" s="3">
         <v>53200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>47300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>55900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>56300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>59200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>59300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>61500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>62400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>62300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>64300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>65600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>34200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>26400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>26100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>23700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>22600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>23300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>25500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>21400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>21000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>16400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>14900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>11700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>13900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>12600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>13100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>13300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>12600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>10700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>7500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>7900</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>7500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1398,162 +1415,168 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>176200</v>
+      </c>
+      <c r="E14" s="3">
         <v>16100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>147400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>36800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>87800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1766500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>61400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>28700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>24700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>29700</v>
-      </c>
-      <c r="M14" s="3">
-        <v>26400</v>
       </c>
       <c r="N14" s="3">
         <v>26400</v>
       </c>
       <c r="O14" s="3">
+        <v>26400</v>
+      </c>
+      <c r="P14" s="3">
         <v>104200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7800</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>10800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>3800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>7300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>8000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>9500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>4600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E15" s="3">
         <v>48000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>47900</v>
-      </c>
-      <c r="F15" s="3">
-        <v>51900</v>
       </c>
       <c r="G15" s="3">
         <v>51900</v>
       </c>
       <c r="H15" s="3">
+        <v>51900</v>
+      </c>
+      <c r="I15" s="3">
         <v>51700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>51200</v>
-      </c>
-      <c r="J15" s="3">
-        <v>51400</v>
       </c>
       <c r="K15" s="3">
         <v>51400</v>
       </c>
       <c r="L15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="M15" s="3">
         <v>50800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>53900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>50500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>21000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7100</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>10</v>
@@ -1567,8 +1590,8 @@
       <c r="U15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1585,8 +1608,8 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>10</v>
+      <c r="AB15" s="3">
+        <v>0</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>10</v>
@@ -1603,14 +1626,14 @@
       <c r="AG15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI15" s="3">
         <v>2500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>2400</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>2300</v>
       </c>
       <c r="AK15" s="3">
         <v>2300</v>
@@ -1618,8 +1641,11 @@
       <c r="AL15" s="3">
         <v>2300</v>
       </c>
+      <c r="AM15" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1655,228 +1681,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>618400</v>
+      </c>
+      <c r="E17" s="3">
         <v>644100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>660800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>675300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>666700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>702500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>641100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>689000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>667300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>716800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>780000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>727000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>557700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>381600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>260100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>227900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>153300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>151100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>192100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>178500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>118100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>123000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>117100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>105800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>103200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>116800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>105100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>101800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>105100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>122600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>111000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>53400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>49300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>54500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>46900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E18" s="3">
         <v>48700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>47000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>51800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-29700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>101500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>55000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>129300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>86500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>56800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>55700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>620700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>376800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>281800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>23300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>224200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>617100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>297600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>83700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>51700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>35100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>20700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>31200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>27600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>15600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>46500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>19200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>5900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1915,50 +1948,51 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3900</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1978,11 +2012,11 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -2025,213 +2059,219 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E21" s="3">
         <v>97800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>99100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>109800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>24900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>65500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>149000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>110800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>55400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>181700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>195800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>164900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>97800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>637500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>391100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>294600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>37800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>236900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>629400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>310000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>94400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>64100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>50100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>33000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>17600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>43100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>39500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>26300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>58600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>16800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>24900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>11100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E22" s="3">
         <v>42300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>44700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>49500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>47800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>46300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>46200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>46600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>44700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>41400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>38100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>29400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4600</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>4800</v>
       </c>
       <c r="AD22" s="3">
         <v>4800</v>
       </c>
       <c r="AE22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AF22" s="3">
         <v>6800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9200</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>2800</v>
       </c>
       <c r="AI22" s="3">
         <v>2800</v>
@@ -2240,233 +2280,242 @@
         <v>2800</v>
       </c>
       <c r="AK22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AL22" s="3">
         <v>3100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-229600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-140900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-162900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1798900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-64400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>60000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>41100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>31300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>42900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>620600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>375400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>281500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>221800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>615500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>295800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>80200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>48800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>32500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>17500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>26600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>22700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-8800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>38700</v>
-      </c>
-      <c r="AG23" s="3">
-        <v>-5300</v>
       </c>
       <c r="AH23" s="3">
         <v>-5300</v>
       </c>
       <c r="AI23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-13800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>16400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E24" s="3">
         <v>3900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>37500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-8900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-15200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-92900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-16200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-11200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>23600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>140700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>84100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>65700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>43700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>145400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>63500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>12500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-9700</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>4700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2575,228 +2624,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-178400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-147700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1706000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-53200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>48800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>30300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>479900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>291300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>215800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>178100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>470100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>232300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>67700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>40200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>30600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>16200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>24800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>32500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>10800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>34000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>14300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-178400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-147700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1706000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-53200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>48800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>30300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>479900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>291300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>215800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>178100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>470100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>232300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>67700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>40200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>30600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>16200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>24800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>32500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>10800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>34000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>14300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2905,8 +2963,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3015,8 +3076,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3125,8 +3189,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3235,50 +3302,53 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E32" s="3">
         <v>1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3900</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -3298,11 +3368,11 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>1100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -3345,118 +3415,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-178400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-147700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1706000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-53200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>48800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>30300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>479900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>291300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>215800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>178100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>470100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>232300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>67700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>40200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>30600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>16200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>24800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>32500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>10800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>34000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>14300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3565,233 +3641,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-178400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-147700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1706000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-53200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>48800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>30300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>479900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>291300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>215800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>178100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>470100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>232300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>67700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>40200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>30600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>16200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>24800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>32500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>10800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>34000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>14300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E38" s="2">
         <v>45746</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45655</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45564</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45200</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45109</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45018</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44927</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44836</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44745</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3830,8 +3915,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3870,118 +3956,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>151700</v>
+      </c>
+      <c r="E41" s="3">
         <v>127100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>98300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>143700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>107000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>78500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>118900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>149300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>178600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>353900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>292900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>212200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>379000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1275500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>802800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>578400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>593200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>981100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>489900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>77500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>72600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>108800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>52800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>28900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>56900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>43700</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>38700</v>
       </c>
       <c r="AE41" s="3">
         <v>38700</v>
       </c>
       <c r="AF41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="AG41" s="3">
         <v>101800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>36100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>173000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>175000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>197500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>169500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3989,46 +4079,46 @@
         <v>900</v>
       </c>
       <c r="E42" s="3">
+        <v>900</v>
+      </c>
+      <c r="F42" s="3">
         <v>1300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>48600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>48800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>45100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>54600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>52100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>51800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>52500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>44300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>25800</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>10</v>
@@ -4045,8 +4135,8 @@
       <c r="W42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -4090,448 +4180,463 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>396900</v>
+      </c>
+      <c r="E43" s="3">
         <v>437000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>451300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>541700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>497300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>476100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>488400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>520200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>426600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>454700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>542100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>557100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>514700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>590000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>393800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>350600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>85600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>105500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>529200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>376100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>120400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>110800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>104900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>86700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>57100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>81100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>76900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>91700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>44700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>92300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>67000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>41600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>19800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>20900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>25000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>578700</v>
+      </c>
+      <c r="E44" s="3">
         <v>563200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>533700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>577000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>602000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>583100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>577800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>551700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>542200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>528600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>524100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>536200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>552700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>181400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>198800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>197000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>218500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>174700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>113800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>95200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>92600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>58700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>58100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>61700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>64600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>66600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>67400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>63300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>59700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>58000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>67100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>23400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>22500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>26000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E45" s="3">
         <v>53700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>57000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>61500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>66500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>163900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>87900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>60200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>21500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>11300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>24900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>16000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>161000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>6500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>4900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1281500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1258200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1218900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1412600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1341300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1212400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1310500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1371300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1308100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1498900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1575100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1445200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1559100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2113700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1440300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1149100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>917700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1282700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1142400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>560900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>296900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>286500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>222200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>185400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>157500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>211600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>193400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>200100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>168000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>268000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>331200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>244500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>225300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>244900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>225400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4544,41 +4649,41 @@
       <c r="F47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3">
         <v>24600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>23400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>24700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>33800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>21000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>15200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>20700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>37900</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>10</v>
@@ -4595,8 +4700,8 @@
       <c r="W47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -4640,79 +4745,82 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1471800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1564400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1548900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1539200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1503900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1621800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1613400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1541600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1553600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1541100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1520000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1425300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1279000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>489300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>476800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>452200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>385900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>307100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>211000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>189800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>172600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>170400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>171900</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>161300</v>
       </c>
       <c r="AA48" s="3">
         <v>161300</v>
@@ -4721,147 +4829,153 @@
         <v>161300</v>
       </c>
       <c r="AC48" s="3">
+        <v>161300</v>
+      </c>
+      <c r="AD48" s="3">
         <v>73900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>70200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>66500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>62900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>61600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>50000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>51000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>49900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>50900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3371600</v>
+      </c>
+      <c r="E49" s="3">
         <v>3368800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3385100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3566500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3568500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3622100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5426300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5419400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5506600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5569800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5600600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5581600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5784500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>428600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>435700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>442700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>446600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>453200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>459500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>465300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>471500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>478300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>485100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>491500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>498200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>505100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>512100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>519000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>526000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>533000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>540900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>118800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>121500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>109100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>111500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4970,8 +5084,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5080,118 +5197,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>254200</v>
+      </c>
+      <c r="E52" s="3">
         <v>270200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>270700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>257100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>226200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>198700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>179600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>179200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>141200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>127000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>139100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>183100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>184600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>40800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>39700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>62400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>57500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>54400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>58300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>33300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>31900</v>
-      </c>
-      <c r="X52" s="3">
-        <v>31600</v>
       </c>
       <c r="Y52" s="3">
         <v>31600</v>
       </c>
       <c r="Z52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="AA52" s="3">
         <v>29400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>29200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>27800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>27000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5300,118 +5423,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6379100</v>
+      </c>
+      <c r="E54" s="3">
         <v>6461600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6423600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6801100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6689200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6703300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8563100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8539100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8550300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8787100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8855800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8655500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8822400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3093100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2430400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2106400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1807700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2097400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1871200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1249400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>972900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>966800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>910900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>867500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>846200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>905900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>806400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>793900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>763500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>865600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>935300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>413800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>398500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>404500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>388300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>376500</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5450,8 +5579,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5490,159 +5620,163 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>218800</v>
+      </c>
+      <c r="E57" s="3">
         <v>230900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>246000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>247200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>237400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>249600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>294800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>253000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>225900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>241500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>283300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>241800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>247300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>157500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>101500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>82700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>99600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>82100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>86300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>49400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>37500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>33200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>26700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>30400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>24800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>26800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>25200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>25700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>21700</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>27300</v>
       </c>
       <c r="AG57" s="3">
         <v>27300</v>
       </c>
       <c r="AH57" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AI57" s="3">
         <v>15700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>11200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>16000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>564200</v>
+      </c>
+      <c r="E58" s="3">
         <v>425000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>372900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>405100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>385900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>189900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>166500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>219300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>233700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>233600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>207500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>207600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>207800</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>10</v>
@@ -5656,47 +5790,47 @@
       <c r="T58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>6700</v>
-      </c>
-      <c r="W58" s="3">
-        <v>12800</v>
       </c>
       <c r="X58" s="3">
         <v>12800</v>
       </c>
       <c r="Y58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="Z58" s="3">
         <v>13100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>21200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>12900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>55400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>54400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>53900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>53400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>94700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>20200</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>100</v>
       </c>
       <c r="AI58" s="3">
         <v>100</v>
@@ -5708,272 +5842,281 @@
         <v>100</v>
       </c>
       <c r="AL58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM58" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>167100</v>
+      </c>
+      <c r="E59" s="3">
         <v>125700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>135700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>134800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>133000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>141400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>175700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>157500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>163600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>250100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>516200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>423300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>444900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>335200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>222000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>214400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>109700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>284800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>250600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>151800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>132700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>90300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>86100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>75600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>74400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>77400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>80200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>78900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>77200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>75300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>80900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>23200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>18600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>17500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1142100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1047200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>998800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1027300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>932400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>779800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>833800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>860000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>790000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>907800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1007000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>872700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>900000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>492700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>323500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>297100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>209300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>366900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>337000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>207900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>183000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>136200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>125900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>127200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>112100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>159600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>159700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>158400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>152300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>197300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>128300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>38900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>31300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>29100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>33600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2237600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2272900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2308500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2374700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2384900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2422800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2454500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2450500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2489700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2588000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2430800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2482000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2533300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5999,159 +6142,165 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>4400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>22800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>37900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>53200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>83200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>81000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>132200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>377300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>152400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>151000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>149700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>148300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E62" s="3">
         <v>48900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>38000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>77800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>54600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>53200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>62800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>51900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>55000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>73300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>483400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>505500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>469500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>185500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>177500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>175200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>187300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>240700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>201500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>192200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>178200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>225400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>220800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>201700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>201300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>247700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>167900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>163800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>161300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>205500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>202500</v>
-      </c>
-      <c r="AH62" s="3">
-        <v>3600</v>
       </c>
       <c r="AI62" s="3">
         <v>3600</v>
       </c>
       <c r="AJ62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AK62" s="3">
         <v>5600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6260,8 +6409,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6370,8 +6522,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6480,118 +6635,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3586400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3464400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3439100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3614400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3515700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3395600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3557200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3572400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3547800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3790600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3921200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3860200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3902800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>678200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>501000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>472300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>396600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>607700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>538500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>400100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>361200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>361600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>351000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>333400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>336200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>445200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>380800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>405400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>394600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>535000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>708100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>194900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>185900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>184400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>187600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6630,8 +6791,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6740,8 +6902,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6850,8 +7015,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6960,8 +7128,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7070,118 +7241,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-132300</v>
+      </c>
+      <c r="E72" s="3">
         <v>123100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>135800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>314200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>334100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>481800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2187800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2180800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2193500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2246700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2197900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2167600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2148400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2129100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1649200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1357900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1142100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1123100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>945000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>474800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>242600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>174900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>134700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>104100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>87900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>86600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>61800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>29300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>18500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-7300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>10000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7290,8 +7467,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7400,8 +7580,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7510,118 +7693,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2792700</v>
+      </c>
+      <c r="E76" s="3">
         <v>2997200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2984500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3186700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3173500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3307700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5005900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4966700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5002500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4996500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4934600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4795300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4919600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2414900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1929400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1634100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1411100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1489700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1332700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>849200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>611700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>605200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>559800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>534200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>510000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>460700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>425600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>388500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>368900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>330600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>227100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>218900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>212600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>220100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>200600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>196700</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7730,233 +7919,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E80" s="2">
         <v>45746</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45655</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45564</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45200</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45109</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45018</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44927</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44836</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44745</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-255400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-178400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-147700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1706000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-53200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>48800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>30300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>479900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>291300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>215800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>178100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>470100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>232300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>67700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>40200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>30600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>16200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>24800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>32500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>10800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>34000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>14300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7995,118 +8193,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E83" s="3">
         <v>63200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>64200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>61700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>63400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>62700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>53700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>116600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>104200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>46000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>15100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>11900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>10700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>11500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>12100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>12900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>6200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5700</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>5200</v>
       </c>
       <c r="AL83" s="3">
         <v>5200</v>
       </c>
+      <c r="AM83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8215,8 +8417,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8325,8 +8530,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8435,8 +8643,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8545,8 +8756,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8655,118 +8869,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="E89" s="3">
         <v>65600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>63700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>117900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-97900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>80400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>41500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>188900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>169400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>224600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>501000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>321400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>77100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-178000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>585500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>439100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>70500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>59000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>61200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>47700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>13300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>40500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>32900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>43200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>50600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>35800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>11200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>29600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>16600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8805,118 +9025,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-56200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-47200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-35300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-66100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-48600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-43400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-51300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-66000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-61700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-30500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-32300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-106900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-75200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-78300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-28800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-22700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4900</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-4700</v>
       </c>
       <c r="AH91" s="3">
         <v>-4700</v>
       </c>
       <c r="AI91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9025,8 +9249,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9135,118 +9362,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-56200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-37900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-56500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-35300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-55100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-42300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-68900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-59300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-29800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1530400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-96000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-93200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-65700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-64600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-27200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-22700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>141700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-404600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9285,8 +9518,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9317,8 +9551,8 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9395,8 +9629,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9505,8 +9742,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9615,8 +9855,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9725,204 +9968,210 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>103300</v>
+      </c>
+      <c r="E100" s="3">
         <v>17600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-68900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-26300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>162500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-57800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-48700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-99700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-59600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-31700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-126000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>413100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-144300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-29600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-43200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-87700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-15500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-62100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-29600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-105200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-111800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>256500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>9900</v>
-      </c>
-      <c r="AI100" s="3">
-        <v>2100</v>
       </c>
       <c r="AJ100" s="3">
         <v>2100</v>
       </c>
       <c r="AK100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AL100" s="3">
         <v>3600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2300</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-100</v>
       </c>
       <c r="Q101" s="3">
         <v>-100</v>
       </c>
       <c r="R101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
       <c r="AC101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD101" s="3">
         <v>200</v>
       </c>
       <c r="AE101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF101" s="3">
         <v>0</v>
@@ -9945,114 +10194,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E102" s="3">
         <v>28700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-45500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>36500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>28500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-40500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-30400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-29700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-175300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>61000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>80700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-167400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-895000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>472800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>224300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-14800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-387800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>491100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>412400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-36200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>56000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>23900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-28400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5000</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-63100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>65700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-136900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>28000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>16100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>QDEL</t>
   </si>
@@ -656,516 +656,528 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="2">
         <v>45928</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45837</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45746</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45655</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45564</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45200</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45109</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45018</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44927</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44836</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44745</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>723600</v>
+      </c>
+      <c r="E8" s="3">
         <v>699900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>613900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>692800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>707800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>727100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>637000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>711000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>742600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>744000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>665100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>846100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>866500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>783800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>613400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1002300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>636900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>509700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>176600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>375300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>809200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>476100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>201800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>174700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>152200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>126500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>108300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>148000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>132600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>117400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>103200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>169100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>114900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>50900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>38300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>73700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>52800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>401900</v>
+      </c>
+      <c r="E9" s="3">
         <v>362800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>339000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>349500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>381700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>374800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>361000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>378900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>360000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>374600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>368600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>397500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>417500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>376300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>275900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>522600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>147500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>136300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>70400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>73400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>107700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>92400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>53000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>59700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>57300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>50600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>49100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>57000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>50500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>47800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>45500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>62900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>60900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>19400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>17800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>23600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>19100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>321700</v>
+      </c>
+      <c r="E10" s="3">
         <v>337100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>274900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>343300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>326100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>352300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>276000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>332100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>382600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>369400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>296500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>448600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>449000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>407500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>337500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>479700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>489400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>373400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>106200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>301900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>701500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>383700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>148800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>115000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>94900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>75900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>59200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>91000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>82100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>69600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>57700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>106200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>54000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>31500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>20500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>50100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>33700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1206,124 +1218,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E12" s="3">
         <v>41500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>45700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>53200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>47300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>55900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>56300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>59200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>59300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>61500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>62400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>62300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>64300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>65600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>34200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>26400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>26100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>23700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>22600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>23300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>25500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>21400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>21000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>16400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>14900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>11700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>13900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>12600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>13100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>13300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>12600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>7500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>7600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>7900</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>7500</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1438,174 +1454,180 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E14" s="3">
         <v>756600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>176200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>16100</v>
       </c>
-      <c r="G14" s="3">
-        <v>147400</v>
-      </c>
       <c r="H14" s="3">
+        <v>116800</v>
+      </c>
+      <c r="I14" s="3">
         <v>36800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>87800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1766500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>61400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>28700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>24700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>29700</v>
-      </c>
-      <c r="O14" s="3">
-        <v>26400</v>
       </c>
       <c r="P14" s="3">
         <v>26400</v>
       </c>
       <c r="Q14" s="3">
+        <v>26400</v>
+      </c>
+      <c r="R14" s="3">
         <v>104200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7800</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>1000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>3300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>7300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>8000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>4600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>2400</v>
       </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E15" s="3">
         <v>47700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>47900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>48000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>47900</v>
-      </c>
-      <c r="H15" s="3">
-        <v>51900</v>
       </c>
       <c r="I15" s="3">
         <v>51900</v>
       </c>
       <c r="J15" s="3">
+        <v>51900</v>
+      </c>
+      <c r="K15" s="3">
         <v>51700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>51200</v>
-      </c>
-      <c r="L15" s="3">
-        <v>51400</v>
       </c>
       <c r="M15" s="3">
         <v>51400</v>
       </c>
       <c r="N15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="O15" s="3">
         <v>50800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>53900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>50500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>21000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7100</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>10</v>
@@ -1619,8 +1641,8 @@
       <c r="W15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1637,8 +1659,8 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>10</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>10</v>
@@ -1655,14 +1677,14 @@
       <c r="AI15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AJ15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK15" s="3">
         <v>2500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>2400</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>2300</v>
       </c>
       <c r="AM15" s="3">
         <v>2300</v>
@@ -1670,8 +1692,11 @@
       <c r="AN15" s="3">
         <v>2300</v>
       </c>
+      <c r="AO15" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1709,240 +1734,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>694600</v>
+      </c>
+      <c r="E17" s="3">
         <v>653200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>618400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>644100</v>
       </c>
-      <c r="G17" s="3">
-        <v>660800</v>
-      </c>
       <c r="H17" s="3">
+        <v>691400</v>
+      </c>
+      <c r="I17" s="3">
         <v>675300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>666700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>702500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>641100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>689000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>667300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>716800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>780000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>727000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>557700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>381600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>260100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>227900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>153300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>151100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>192100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>178500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>118100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>123000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>117100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>105800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>103200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>116800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>105100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>101800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>105100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>122600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>111000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>53400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>49300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>54500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>46900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E18" s="3">
         <v>46700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>48700</v>
       </c>
-      <c r="G18" s="3">
-        <v>47000</v>
-      </c>
       <c r="H18" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I18" s="3">
         <v>51800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-29700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>101500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>55000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>129300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>86500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>56800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>55700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>620700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>376800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>281800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>23300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>224200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>617100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>297600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>83700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>51700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>35100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>20700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>31200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>27600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>15600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>46500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>19200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>5900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1983,56 +2015,57 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3900</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -2052,11 +2085,11 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -2099,225 +2132,231 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E21" s="3">
         <v>96000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>37500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>97800</v>
       </c>
-      <c r="G21" s="3">
-        <v>99100</v>
-      </c>
       <c r="H21" s="3">
+        <v>68500</v>
+      </c>
+      <c r="I21" s="3">
         <v>109800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>24900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>65500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>149000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>110800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>55400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>181700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>195800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>164900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>97800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>637500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>391100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>294600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>37800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>236900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>629400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>310000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>94400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>64100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>50100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>33000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>17600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>43100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>39500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>26300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>58600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>16800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>24900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>11100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E22" s="3">
         <v>47800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>42900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>42300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>44700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>49500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>47800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>46300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>46200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>46600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>44700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>41400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>38100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>29400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4600</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>4800</v>
       </c>
       <c r="AF22" s="3">
         <v>4800</v>
       </c>
       <c r="AG22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AH22" s="3">
         <v>6800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9200</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>2800</v>
       </c>
       <c r="AK22" s="3">
         <v>2800</v>
@@ -2326,245 +2365,254 @@
         <v>2800</v>
       </c>
       <c r="AM22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AN22" s="3">
         <v>3100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-112400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-756900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-229600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-140900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-28800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-162900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1798900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-64400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>60000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>41100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>31300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>42900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>620600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>375400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>281500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>21700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>221800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>615500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>295800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>80200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>48800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>32500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>17500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>26600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>22700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-8800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>38700</v>
-      </c>
-      <c r="AI23" s="3">
-        <v>-5300</v>
       </c>
       <c r="AJ23" s="3">
         <v>-5300</v>
       </c>
       <c r="AK23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AL23" s="3">
         <v>-13800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>16400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-23900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>25800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>37500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-8900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-15200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-92900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-16200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-11200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>12100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>23600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>140700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>84100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>65700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>43700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>145400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>63500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>8600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-9700</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>2100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>4700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2679,240 +2727,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-733000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-255400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-178400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-147700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1706000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-53200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>48800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>479900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>291300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>215800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>178100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>470100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>232300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>67700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>40200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>30600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>16200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>24800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>32500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>10800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>34000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>14300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-733000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-255400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-178400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-147700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1706000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-53200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>48800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>30300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>479900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>291300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>215800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>19100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>178100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>470100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>232300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>67700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>40200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>30600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>16200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>24800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>32500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>10800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>34000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>14300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3027,8 +3084,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3143,8 +3203,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3259,8 +3322,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3375,56 +3441,59 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3900</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3444,11 +3513,11 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -3491,124 +3560,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-733000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-255400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-178400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-147700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1706000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-53200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>48800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>30300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>479900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>291300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>215800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>178100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>470100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>232300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>67700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>40200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>30600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>16200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>24800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>32500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>10800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>34000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>14300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3723,245 +3798,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-733000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-255400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-178400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-147700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1706000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-53200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>48800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>30300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>479900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>291300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>215800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>178100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>470100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>232300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>67700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>40200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>30600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>16200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>24800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>32500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>10800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>34000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>14300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E38" s="2">
         <v>45928</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45837</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45746</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45655</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45564</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45200</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45109</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45018</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44927</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44836</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44745</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4002,8 +4086,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4044,129 +4129,133 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>169800</v>
+      </c>
+      <c r="E41" s="3">
         <v>98100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>151700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>127100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>98300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>143700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>107000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>78500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>118900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>149300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>178600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>353900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>292900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>212200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>379000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1275500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>802800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>578400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>593200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>981100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>489900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>77500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>72600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>108800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>52800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>28900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>28600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>56900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>43700</v>
-      </c>
-      <c r="AF41" s="3">
-        <v>38700</v>
       </c>
       <c r="AG41" s="3">
         <v>38700</v>
       </c>
       <c r="AH41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="AI41" s="3">
         <v>101800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>36100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>173000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>175000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>197500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>169500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="E42" s="3">
         <v>900</v>
@@ -4175,46 +4264,46 @@
         <v>900</v>
       </c>
       <c r="G42" s="3">
+        <v>900</v>
+      </c>
+      <c r="H42" s="3">
         <v>1300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>48600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>48800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>45100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>54600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>52100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>51800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>52500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>44300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>25800</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>10</v>
@@ -4231,8 +4320,8 @@
       <c r="Y42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -4276,472 +4365,487 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>571700</v>
+      </c>
+      <c r="E43" s="3">
         <v>513000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>396900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>437000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>451300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>541700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>497300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>476100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>488400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>520200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>426600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>454700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>542100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>557100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>514700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>590000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>393800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>350600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>85600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>105500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>529200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>376100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>120400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>110800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>104900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>86700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>57100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>81100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>76900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>91700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>44700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>92300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>67000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>41600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>19800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>20900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>25000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>577600</v>
+      </c>
+      <c r="E44" s="3">
         <v>613800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>578700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>563200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>533700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>577000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>602000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>583100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>577800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>551700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>542200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>528600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>524100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>536200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>552700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>181400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>198800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>197000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>218500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>174700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>113800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>95200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>92600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>58700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>58100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>61700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>64600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>66600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>67400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>63300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>59700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>58000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>67100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>23400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>23000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>22500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>26000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E45" s="3">
         <v>69100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>87000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>53700</v>
       </c>
-      <c r="G45" s="3">
-        <v>57000</v>
-      </c>
       <c r="H45" s="3">
+        <v>61100</v>
+      </c>
+      <c r="I45" s="3">
         <v>61500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>66500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>163900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>87900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>60200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>20300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>21500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>11300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>24900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>16000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>161000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>6500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>7400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1447300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1366700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1281500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1258200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1218900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1412600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1341300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1212400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1310500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1371300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1308100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1498900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1575100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1445200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1559100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2113700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1440300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1149100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>917700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1282700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1142400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>560900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>296900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>286500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>222200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>185400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>157500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>211600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>193400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>200100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>168000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>268000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>331200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>244500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>225300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>244900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>225400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4757,44 +4861,44 @@
       <c r="G47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="3">
+        <v>12400</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>24600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>23400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>24700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>33800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>21000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>20300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>15200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>20700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>37900</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>10</v>
@@ -4811,8 +4915,8 @@
       <c r="Y47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -4856,85 +4960,88 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1513800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1480300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1471800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1564400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1548900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1539200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1503900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1621800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1613400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1541600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1553600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1541100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1520000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1425300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1279000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>489300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>476800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>452200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>385900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>307100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>211000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>189800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>172600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>170400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>171900</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>161300</v>
       </c>
       <c r="AC48" s="3">
         <v>161300</v>
@@ -4943,153 +5050,159 @@
         <v>161300</v>
       </c>
       <c r="AE48" s="3">
+        <v>161300</v>
+      </c>
+      <c r="AF48" s="3">
         <v>73900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>70200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>66500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>62900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>61600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>50000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>51000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>49900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>50900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2563800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2608000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3371600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3368800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3385100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3566500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3568500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3622100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5426300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5419400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5506600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5569800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5600600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5581600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5784500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>428600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>435700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>442700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>446600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>453200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>459500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>465300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>471500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>478300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>485100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>491500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>498200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>505100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>512100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>519000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>526000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>533000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>540900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>118800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>121500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>109100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>111500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5204,8 +5317,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5320,124 +5436,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>244400</v>
+      </c>
+      <c r="E52" s="3">
         <v>220100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>254200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>270200</v>
       </c>
-      <c r="G52" s="3">
-        <v>270700</v>
-      </c>
       <c r="H52" s="3">
+        <v>258300</v>
+      </c>
+      <c r="I52" s="3">
         <v>257100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>226200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>198700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>179600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>179200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>141200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>127000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>139100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>183100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>184600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>40800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>39700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>62400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>57500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>54400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>58300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>33300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>31900</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>31600</v>
       </c>
       <c r="AA52" s="3">
         <v>31600</v>
       </c>
       <c r="AB52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="AC52" s="3">
         <v>29400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>29200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>27800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>27000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5552,124 +5674,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5769300</v>
+      </c>
+      <c r="E54" s="3">
         <v>5675100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6379100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6461600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6423600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6801100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6689200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6703300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8563100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8539100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8550300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8787100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8855800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8655500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8822400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3093100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2430400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2106400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1807700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2097400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1871200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1249400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>972900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>966800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>910900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>867500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>846200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>905900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>806400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>793900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>763500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>865600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>935300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>413800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>398500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>404500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>388300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>376500</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5710,8 +5838,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5752,171 +5881,175 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>279400</v>
+      </c>
+      <c r="E57" s="3">
         <v>213700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>218800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>230900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>246000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>247200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>237400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>249600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>294800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>253000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>225900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>241500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>283300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>241800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>247300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>157500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>101500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>82700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>99600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>82100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>86300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>49400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>37500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>33200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>26700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>30400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>24800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>26800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>25200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>25700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>21700</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>27300</v>
       </c>
       <c r="AI57" s="3">
         <v>27300</v>
       </c>
       <c r="AJ57" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AK57" s="3">
         <v>15700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>11200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>10400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>16000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>207600</v>
+      </c>
+      <c r="E58" s="3">
         <v>191800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>564200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>425000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>372900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>405100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>385900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>189900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>166500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>219300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>233700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>233600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>207500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>207600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>207800</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>10</v>
@@ -5930,47 +6063,47 @@
       <c r="V58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>6700</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>12800</v>
       </c>
       <c r="Z58" s="3">
         <v>12800</v>
       </c>
       <c r="AA58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="AB58" s="3">
         <v>13100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>21200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>12900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>55400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>54400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>53900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>53400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>94700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>20200</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>100</v>
       </c>
       <c r="AK58" s="3">
         <v>100</v>
@@ -5982,290 +6115,299 @@
         <v>100</v>
       </c>
       <c r="AN58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO58" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>187800</v>
+      </c>
+      <c r="E59" s="3">
         <v>120700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>167100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>125700</v>
       </c>
-      <c r="G59" s="3">
-        <v>135700</v>
-      </c>
       <c r="H59" s="3">
+        <v>114300</v>
+      </c>
+      <c r="I59" s="3">
         <v>134800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>133000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>141400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>175700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>157500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>163600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>250100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>516200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>423300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>444900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>335200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>222000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>214400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>109700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>284800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>250600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>151800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>132700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>90300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>86100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>75600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>74400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>77400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>80200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>78900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>77200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>75300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>80900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>23200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>20000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>18600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>17500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>966100</v>
+      </c>
+      <c r="E60" s="3">
         <v>767900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1142100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1047200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>998800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1027300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>932400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>779800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>833800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>860000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>790000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>907800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1007000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>872700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>900000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>492700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>323500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>297100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>209300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>366900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>337000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>207900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>183000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>136200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>125900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>127200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>112100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>159600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>159700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>158400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>152300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>197300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>128300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>38900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>31300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>29100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>33600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2646200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2673300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2237600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2272900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2308500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2374700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2384900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2422800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2454500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2450500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2489700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2588000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2430800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2482000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2533300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -6291,165 +6433,171 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>4400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>22800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>37900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>53200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>83200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>81000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>132200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>377300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>152400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>151000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>149700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>148300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>129600</v>
+      </c>
+      <c r="E62" s="3">
         <v>100500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>106800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>48900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>38000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>77800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>54600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>53200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>62800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>51900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>55000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>73300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>483400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>505500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>469500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>185500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>177500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>175200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>187300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>240700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>201500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>192200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>178200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>225400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>220800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>201700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>201300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>247700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>167900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>163800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>161300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>205500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>202500</v>
-      </c>
-      <c r="AJ62" s="3">
-        <v>3600</v>
       </c>
       <c r="AK62" s="3">
         <v>3600</v>
       </c>
       <c r="AL62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AM62" s="3">
         <v>5600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>5700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6564,8 +6712,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6680,8 +6831,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6796,124 +6950,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3848800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3638700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3586400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3464400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3439100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3614400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3515700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3395600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3557200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3572400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3547800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3790600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3921200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3860200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3902800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>678200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>501000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>472300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>396600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>607700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>538500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>400100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>361200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>361600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>351000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>333400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>336200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>445200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>380800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>405400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>394600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>535000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>708100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>194900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>185900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>184400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>187600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6954,8 +7114,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7070,8 +7231,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7186,8 +7350,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7302,8 +7469,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7418,124 +7588,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-996000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-865300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-132300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>123100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>135800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>314200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>334100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>481800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2187800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2180800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2193500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2246700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2197900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2167600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2148400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2129100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1649200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1357900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1142100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1123100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>945000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>474800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>242600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>174900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>134700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>104100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>87900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>86600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>61800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>29300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>21500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-7300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>10000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7650,8 +7826,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7766,8 +7945,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7882,124 +8064,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1920500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2036400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2792700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2997200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2984500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3186700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3173500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3307700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5005900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4966700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5002500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4996500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4934600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4795300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4919600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2414900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1929400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1634100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1411100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1489700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1332700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>849200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>611700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>605200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>559800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>534200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>510000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>460700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>425600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>388500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>368900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>330600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>227100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>218900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>212600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>220100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>200600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>196700</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8114,245 +8302,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E80" s="2">
         <v>45928</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45837</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45746</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45655</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45564</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45200</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45109</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45018</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44927</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44836</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44745</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-130700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-733000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-255400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-178400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-147700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1706000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-53200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>48800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>30300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>479900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>291300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>215800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>178100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>470100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>232300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>67700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>40200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>30600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>16200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>24800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>32500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>10800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>34000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>14300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8393,124 +8590,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>61400</v>
+      </c>
+      <c r="E83" s="3">
         <v>61200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>64200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>63200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>64200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>61700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>63100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>63400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>62700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>53700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>116600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>104200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>46000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>16800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>11900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>15100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>12300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>11900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>10700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>11500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>12100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>6200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>5900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>5700</v>
-      </c>
-      <c r="AM83" s="3">
-        <v>5200</v>
       </c>
       <c r="AN83" s="3">
         <v>5200</v>
       </c>
+      <c r="AO83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8625,8 +8826,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8741,8 +8945,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8857,8 +9064,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8973,8 +9183,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9089,124 +9302,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>131900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-45500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-46800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>65600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>63700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>117900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-97900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>80400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>41500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-30600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>188900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>169400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>224600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>501000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>321400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>77100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-178000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>585500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>439100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>70500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>59000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>61200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>47700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>13300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>40500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>32900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>43200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>50600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>35800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>11200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>29600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>16600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9247,124 +9466,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-45300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-49200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-37500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-56200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-47200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-46500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-35300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-66100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-48600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-51300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-66000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-61700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-32300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-106900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-75200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-78300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-28800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-22700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-9300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4900</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>-4700</v>
       </c>
       <c r="AJ91" s="3">
         <v>-4700</v>
       </c>
       <c r="AK91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9479,8 +9702,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9595,124 +9821,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-53900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-56200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-37900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-56500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-35300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-20200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-55100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-42300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-68900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-59300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-29800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1530400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-24700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-96000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-93200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-65700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-64600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-27200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-22700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>141700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-404600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9753,8 +9985,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9791,8 +10024,8 @@
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9869,8 +10102,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9985,8 +10221,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10101,8 +10340,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10217,216 +10459,222 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E100" s="3">
         <v>46000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>103300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-68900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-26300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>162500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-57800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-48700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-99700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-59600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-31700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-126000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>413100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-144300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-29600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-43200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-87700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-62100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-29600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-105200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-111800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>256500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>9900</v>
-      </c>
-      <c r="AK100" s="3">
-        <v>2100</v>
       </c>
       <c r="AL100" s="3">
         <v>2100</v>
       </c>
       <c r="AM100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AN100" s="3">
         <v>3600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2300</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-100</v>
       </c>
       <c r="S101" s="3">
         <v>-100</v>
       </c>
       <c r="T101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
       <c r="AE101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AF101" s="3">
         <v>200</v>
       </c>
       <c r="AG101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AH101" s="3">
         <v>0</v>
@@ -10449,120 +10697,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-53600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>28700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-45500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>36500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>28500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-40500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-29700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-175300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>61000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>80700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-167400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-895000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>472800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>224300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-14800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-387800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>491100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>412400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-36200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>56000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>23900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-28400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>13200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>5000</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-63100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>65700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-136900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-22400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>28000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>16100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-2200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/QDEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>QDEL</t>
   </si>
@@ -656,528 +656,541 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E7" s="2">
         <v>46019</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45928</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45837</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45746</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45655</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45564</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45200</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45109</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45018</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44927</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44836</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44745</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>619800</v>
+      </c>
+      <c r="E8" s="3">
         <v>723600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>699900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>613900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>692800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>707800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>727100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>637000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>711000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>742600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>744000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>665100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>846100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>866500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>783800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>613400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1002300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>636900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>509700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>176600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>375300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>809200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>476100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>201800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>174700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>152200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>126500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>108300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>148000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>132600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>117400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>103200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>169100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>114900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>50900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>38300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>73700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>52800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>354000</v>
+      </c>
+      <c r="E9" s="3">
         <v>401900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>362800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>339000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>349500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>381700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>374800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>361000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>378900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>360000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>374600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>368600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>397500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>417500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>376300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>275900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>522600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>147500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>136300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>70400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>73400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>107700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>92400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>53000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>59700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>57300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>50600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>49100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>57000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>50500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>47800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>45500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>62900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>60900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>19400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>17800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>23600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>19100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>265800</v>
+      </c>
+      <c r="E10" s="3">
         <v>321700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>337100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>274900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>343300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>326100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>352300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>276000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>332100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>382600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>369400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>296500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>448600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>449000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>407500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>337500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>479700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>489400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>373400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>106200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>301900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>701500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>383700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>148800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>115000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>94900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>75900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>59200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>91000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>82100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>69600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>57700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>106200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>54000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>31500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>20500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>50100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>33700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1219,127 +1232,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E12" s="3">
         <v>45800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>41500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>45700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>53200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>47300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>55900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>56300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>59200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>59300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>61500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>62400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>62300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>64300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>65600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>34200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>26400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>26100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>23700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>22600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>23300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>25500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>21400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>21000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>16400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>14900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>12000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>11700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>13900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>12600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>13100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>13300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>10700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>7500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>7600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>7900</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>7500</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1457,180 +1474,186 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E14" s="3">
         <v>95300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>756600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>176200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>16100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>116800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>36800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>87800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1766500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>61400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>28700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>24700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>29700</v>
-      </c>
-      <c r="P14" s="3">
-        <v>26400</v>
       </c>
       <c r="Q14" s="3">
         <v>26400</v>
       </c>
       <c r="R14" s="3">
+        <v>26400</v>
+      </c>
+      <c r="S14" s="3">
         <v>104200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7800</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>1000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>9500</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>4600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>2400</v>
       </c>
-      <c r="AM14" s="3" t="s">
+      <c r="AN14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E15" s="3">
         <v>45600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>47700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>47900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>48000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>47900</v>
-      </c>
-      <c r="I15" s="3">
-        <v>51900</v>
       </c>
       <c r="J15" s="3">
         <v>51900</v>
       </c>
       <c r="K15" s="3">
+        <v>51900</v>
+      </c>
+      <c r="L15" s="3">
         <v>51700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>51200</v>
-      </c>
-      <c r="M15" s="3">
-        <v>51400</v>
       </c>
       <c r="N15" s="3">
         <v>51400</v>
       </c>
       <c r="O15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="P15" s="3">
         <v>50800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>53900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>50500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>21000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7100</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>10</v>
@@ -1644,8 +1667,8 @@
       <c r="X15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1662,8 +1685,8 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>10</v>
+      <c r="AE15" s="3">
+        <v>0</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>10</v>
@@ -1680,14 +1703,14 @@
       <c r="AJ15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL15" s="3">
         <v>2500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>2400</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>2300</v>
       </c>
       <c r="AN15" s="3">
         <v>2300</v>
@@ -1695,8 +1718,11 @@
       <c r="AO15" s="3">
         <v>2300</v>
       </c>
+      <c r="AP15" s="3">
+        <v>2300</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1735,246 +1761,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>645200</v>
+      </c>
+      <c r="E17" s="3">
         <v>694600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>653200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>618400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>644100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>691400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>675300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>666700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>702500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>641100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>689000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>667300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>716800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>780000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>727000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>557700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>381600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>260100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>227900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>153300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>151100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>192100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>178500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>118100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>123000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>117100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>105800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>103200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>116800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>105100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>101800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>105100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>122600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>111000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>53400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>49300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>54500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>46900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E18" s="3">
         <v>29000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>48700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>51800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-29700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>101500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>55000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>129300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>86500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>56800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>55700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>620700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>376800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>281800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>23300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>224200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>617100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>297600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>83700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>51700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>35100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>20700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>31200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>27600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>15600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-11000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>19200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>5900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2016,59 +2049,60 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3900</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -2088,11 +2122,11 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -2135,231 +2169,237 @@
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E21" s="3">
         <v>80000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>96000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>37500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>97800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>68500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>109800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>24900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>65500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>149000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>110800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>55400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>181700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>195800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>164900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>97800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>637500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>391100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>294600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>37800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>236900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>629400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>310000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>94400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>64100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>50100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>33000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>17600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>43100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>39500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>26300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>16800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-5100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>24900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>11100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E22" s="3">
         <v>50100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>47800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>42900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>42300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>44700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>49500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>47800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>46300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>46200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>46600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>44700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>41400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>38100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>29400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>2800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4600</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>4800</v>
       </c>
       <c r="AG22" s="3">
         <v>4800</v>
       </c>
       <c r="AH22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AI22" s="3">
         <v>6800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>9200</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>2800</v>
       </c>
       <c r="AL22" s="3">
         <v>2800</v>
@@ -2368,251 +2408,260 @@
         <v>2800</v>
       </c>
       <c r="AN22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AO22" s="3">
         <v>3100</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-112400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-756900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-229600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-140900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-162900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1798900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-64400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>60000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>41100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>31300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>42900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>620600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>375400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>281500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>21700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>221800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>615500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>295800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>80200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>48800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>32500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>17500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>26600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>22700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-8800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>38700</v>
-      </c>
-      <c r="AJ23" s="3">
-        <v>-5300</v>
       </c>
       <c r="AK23" s="3">
         <v>-5300</v>
       </c>
       <c r="AL23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="AM23" s="3">
         <v>-13800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>16400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E24" s="3">
         <v>18300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-23900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>25800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>37500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-8900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-15200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-92900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-16200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-11200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>23600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>140700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>84100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>65700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>43700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>145400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>63500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>8600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>2100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>4700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2730,246 +2779,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-91800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-130700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-733000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-255400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-178400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-147700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1706000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-53200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>48800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>479900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>291300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>215800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>178100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>470100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>232300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>67700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>40200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>30600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>16200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>24800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>32500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>10800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>14300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-91800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-130700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-733000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-255400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-178400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-147700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1706000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-53200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>48800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>479900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>291300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>215800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>178100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>470100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>232300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>67700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>40200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>30600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>16200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>24800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>32500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>10800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-5100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>14300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3087,8 +3145,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3206,8 +3267,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3325,8 +3389,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3444,59 +3511,62 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>5400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3900</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3516,11 +3586,11 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -3563,127 +3633,133 @@
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-91800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-130700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-733000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-255400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-178400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-147700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1706000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-53200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>48800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>479900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>291300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>215800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>178100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>470100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>232300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>67700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>40200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>30600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>16200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>24800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>32500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>10800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-5100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>14300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3801,251 +3877,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-91800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-130700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-733000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-255400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-178400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-147700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1706000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-53200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>48800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>479900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>291300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>215800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>178100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>470100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>232300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>67700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>40200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>30600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>16200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>24800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>32500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>10800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-5100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>14300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E38" s="2">
         <v>46019</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45928</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45837</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45746</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45655</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45564</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45200</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45109</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45018</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44927</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44836</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44745</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4087,8 +4172,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4130,135 +4216,139 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>140400</v>
+      </c>
+      <c r="E41" s="3">
         <v>169800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>98100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>151700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>127100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>98300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>143700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>107000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>78500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>118900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>149300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>178600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>353900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>292900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>212200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>379000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1275500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>802800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>578400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>593200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>981100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>489900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>77500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>72600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>108800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>52800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>28900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>28600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>56900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>43700</v>
-      </c>
-      <c r="AG41" s="3">
-        <v>38700</v>
       </c>
       <c r="AH41" s="3">
         <v>38700</v>
       </c>
       <c r="AI41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>101800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>36100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>173000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>175000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>197500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>169500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>153400</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>300</v>
-      </c>
-      <c r="E42" s="3">
-        <v>900</v>
       </c>
       <c r="F42" s="3">
         <v>900</v>
@@ -4267,46 +4357,46 @@
         <v>900</v>
       </c>
       <c r="H42" s="3">
+        <v>900</v>
+      </c>
+      <c r="I42" s="3">
         <v>1300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>48600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>48800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>45100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>54600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>52100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>51800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>52500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>44300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>25800</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>10</v>
@@ -4323,8 +4413,8 @@
       <c r="Z42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -4368,489 +4458,504 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>486700</v>
+      </c>
+      <c r="E43" s="3">
         <v>571700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>513000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>396900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>437000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>451300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>541700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>497300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>476100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>488400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>520200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>426600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>454700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>542100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>557100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>514700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>590000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>393800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>350600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>85600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>105500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>529200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>376100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>120400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>110800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>104900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>86700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>57100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>81100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>76900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>91700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>44700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>92300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>67000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>41600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>19800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>20900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>25000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>26200</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>611500</v>
+      </c>
+      <c r="E44" s="3">
         <v>577600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>613800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>578700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>563200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>533700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>577000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>602000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>583100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>577800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>551700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>542200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>528600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>524100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>536200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>552700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>181400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>198800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>197000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>218500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>174700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>113800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>95200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>92600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>58700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>58100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>61700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>64600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>66600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>67400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>63300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>59700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>58000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>67100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>23400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>23000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>22500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>26000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>23400</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E45" s="3">
         <v>74000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>69100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>87000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>53700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>61100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>61500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>66500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>163900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>87900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>60200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>22500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>21500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>8000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>6900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>6400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>24900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>161000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>6500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>7400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>4900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>5600</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1377000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1447300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1366700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1281500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1258200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1218900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1412600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1341300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1212400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1310500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1371300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1308100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1498900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1575100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1445200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1559100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2113700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1440300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1149100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>917700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1282700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1142400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>560900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>296900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>286500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>222200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>185400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>157500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>211600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>193400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>200100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>168000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>268000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>331200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>244500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>225300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>244900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>225400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>10</v>
+      <c r="D47" s="3">
+        <v>1000</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>10</v>
@@ -4861,47 +4966,47 @@
       <c r="G47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3">
         <v>12400</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>24600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>23400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>24700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>33800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>21000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>20300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>15200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>20700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>37900</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>10</v>
@@ -4918,8 +5023,8 @@
       <c r="Z47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -4963,88 +5068,91 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1497300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1513800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1480300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1471800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1564400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1548900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1539200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1503900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1621800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1613400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1541600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1553600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1541100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1520000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1425300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1279000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>489300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>476800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>452200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>385900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>307100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>211000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>189800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>172600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>170400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>171900</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>161300</v>
       </c>
       <c r="AD48" s="3">
         <v>161300</v>
@@ -5053,156 +5161,162 @@
         <v>161300</v>
       </c>
       <c r="AF48" s="3">
+        <v>161300</v>
+      </c>
+      <c r="AG48" s="3">
         <v>73900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>70200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>66500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>62900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>61600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>50000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>51000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>49900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>50900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2520200</v>
+      </c>
+      <c r="E49" s="3">
         <v>2563800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2608000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3371600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3368800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3385100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3566500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3568500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3622100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5426300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5419400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5506600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5569800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5600600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5581600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5784500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>428600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>435700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>442700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>446600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>453200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>459500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>465300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>471500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>478300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>485100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>491500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>498200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>505100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>512100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>519000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>526000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>533000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>540900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>118800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>121500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>109100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>111500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>112500</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5320,8 +5434,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5439,127 +5556,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>233200</v>
+      </c>
+      <c r="E52" s="3">
         <v>244400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>220100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>254200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>270200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>258300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>257100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>226200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>198700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>179600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>179200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>141200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>127000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>139100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>183100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>184600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>40800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>39700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>62400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>57500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>54400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>58300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>33300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>31900</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>31600</v>
       </c>
       <c r="AB52" s="3">
         <v>31600</v>
       </c>
       <c r="AC52" s="3">
+        <v>31600</v>
+      </c>
+      <c r="AD52" s="3">
         <v>29400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>29200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>27800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>27000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5677,127 +5800,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5628700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5769300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5675100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6379100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6461600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6423600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6801100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6689200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6703300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8563100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8539100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8550300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8787100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8855800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8655500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8822400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3093100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2430400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2106400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1807700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2097400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1871200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1249400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>972900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>966800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>910900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>867500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>846200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>905900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>806400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>793900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>763500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>865600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>935300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>413800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>398500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>404500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>388300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>376500</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5839,8 +5968,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5882,177 +6012,181 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>243500</v>
+      </c>
+      <c r="E57" s="3">
         <v>279400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>213700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>218800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>230900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>246000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>247200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>237400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>249600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>294800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>253000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>225900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>241500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>283300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>241800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>247300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>157500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>101500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>82700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>99600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>82100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>86300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>49400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>37500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>33200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>26700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>30400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>24800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>26800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>25200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>25700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>21700</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>27300</v>
       </c>
       <c r="AJ57" s="3">
         <v>27300</v>
       </c>
       <c r="AK57" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AL57" s="3">
         <v>15700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>11200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>10400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>16000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>259500</v>
+      </c>
+      <c r="E58" s="3">
         <v>207600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>191800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>564200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>425000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>372900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>405100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>385900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>189900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>166500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>219300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>233700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>233600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>207500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>207600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>207800</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>10</v>
@@ -6066,47 +6200,47 @@
       <c r="W58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>6700</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>12800</v>
       </c>
       <c r="AA58" s="3">
         <v>12800</v>
       </c>
       <c r="AB58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="AC58" s="3">
         <v>13100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>21200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>12900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>55400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>54400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>53900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>53400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>94700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>20200</v>
-      </c>
-      <c r="AK58" s="3">
-        <v>100</v>
       </c>
       <c r="AL58" s="3">
         <v>100</v>
@@ -6118,299 +6252,308 @@
         <v>100</v>
       </c>
       <c r="AO58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP58" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>207700</v>
+      </c>
+      <c r="E59" s="3">
         <v>187800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>120700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>167100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>125700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>114300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>134800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>133000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>141400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>175700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>157500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>163600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>250100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>516200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>423300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>444900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>335200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>222000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>214400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>109700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>284800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>250600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>151800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>132700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>90300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>86100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>75600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>74400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>77400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>80200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>78900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>77200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>75300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>80900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>23200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>20000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>18600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>17500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>13400</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>962400</v>
+      </c>
+      <c r="E60" s="3">
         <v>966100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>767900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1142100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1047200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>998800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1027300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>932400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>779800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>833800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>860000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>790000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>907800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1007000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>872700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>900000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>492700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>323500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>297100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>209300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>366900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>337000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>207900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>183000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>136200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>125900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>127200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>112100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>159600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>159700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>158400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>152300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>197300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>128300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>38900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>31300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>29100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>33600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2615200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2646200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2673300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2237600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2272900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2308500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2374700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2384900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2422800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2454500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2450500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2489700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2588000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2430800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2482000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2533300</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -6436,168 +6579,174 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>4400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>22800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>37900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>53200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>83200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>81000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>132200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>377300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>152400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>151000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>149700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>148300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>95700</v>
+      </c>
+      <c r="E62" s="3">
         <v>129600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>100500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>106800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>48900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>77800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>54600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>53200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>62800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>51900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>55000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>73300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>483400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>505500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>469500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>185500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>177500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>175200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>187300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>240700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>201500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>192200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>178200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>225400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>220800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>201700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>201300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>247700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>167900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>163800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>161300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>205500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>202500</v>
-      </c>
-      <c r="AK62" s="3">
-        <v>3600</v>
       </c>
       <c r="AL62" s="3">
         <v>3600</v>
       </c>
       <c r="AM62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AN62" s="3">
         <v>5600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>5700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>7900</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6715,8 +6864,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6834,8 +6986,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6953,127 +7108,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3777300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3848800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3638700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3586400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3464400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3439100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3614400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3515700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3395600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3557200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3572400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3547800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3790600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3921200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3860200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3902800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>678200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>501000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>472300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>396600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>607700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>538500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>400100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>361200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>361600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>351000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>333400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>336200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>445200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>380800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>405400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>394600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>535000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>708100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>194900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>185900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>184400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>187600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>179800</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7115,8 +7276,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7234,8 +7396,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7353,8 +7518,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7472,8 +7640,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7591,127 +7762,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1087800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-996000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-865300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-132300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>123100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>135800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>314200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>334100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>481800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2187800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2180800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2193500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2246700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2197900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2167600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2148400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2129100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1649200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1357900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1142100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1123100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>945000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>474800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>242600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>174900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>134700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>104100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>87900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>86600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>61800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>29300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>21500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-12400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-7300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-1800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>10000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-4300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7829,8 +8006,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7948,8 +8128,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8067,127 +8250,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1851400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1920500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2036400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2792700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2997200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2984500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3186700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3173500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3307700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5005900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4966700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5002500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4996500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4934600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4795300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4919600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2414900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1929400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1634100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1411100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1489700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1332700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>849200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>611700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>605200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>559800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>534200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>510000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>460700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>425600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>388500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>368900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>330600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>227100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>218900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>212600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>220100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>200600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>196700</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8305,251 +8494,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E80" s="2">
         <v>46019</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45928</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45837</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45746</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45655</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45564</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45200</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45109</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45018</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44927</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44836</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44745</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-91800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-130700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-733000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-255400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-178400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-147700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1706000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-53200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>48800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>479900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>291300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>215800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>178100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>470100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>232300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>67700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>40200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>30600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>16200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>24800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>32500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>10800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-5100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>14300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8591,127 +8789,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E83" s="3">
         <v>61400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>61200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>64200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>64200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>61700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>63100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>63400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>62700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>53700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>116600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>104200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>46000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>16800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>11900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>12300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>12500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>12000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>11900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>10700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>11500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>12900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>6200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>5900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>5700</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>5200</v>
       </c>
       <c r="AO83" s="3">
         <v>5200</v>
       </c>
+      <c r="AP83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8829,8 +9031,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8948,8 +9153,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9067,8 +9275,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9186,8 +9397,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9305,127 +9519,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E89" s="3">
         <v>131900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-45500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-46800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>65600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>63700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>117900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-97900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>80400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>41500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>188900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>169400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>224600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>501000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>321400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>77100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-178000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>585500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>439100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>70500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>59000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>61200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>47700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>13300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>40500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>32900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>43200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>50600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>35800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>11200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-7500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-5600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>29600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>16600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9467,127 +9687,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-45300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-49200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-37500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-56200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-47200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-46500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-35300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-66100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-48600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-43400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-51300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-66000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-61700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-30500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-22400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-32300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-106900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-75200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-78300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-28800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-22700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-9300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4900</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>-4700</v>
       </c>
       <c r="AK91" s="3">
         <v>-4700</v>
       </c>
       <c r="AL91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9705,8 +9929,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9824,127 +10051,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-49600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-53900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-33000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-56200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-37900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-56500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-35300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-55100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-42300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-68900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-59300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-29800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1530400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-24700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-96000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-93200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-65700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-64600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-27200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-22700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-8600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>141700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-404600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-4400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-19000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-4000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9986,8 +10219,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10027,8 +10261,8 @@
       <c r="O96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10105,8 +10339,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10224,8 +10461,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10343,8 +10583,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10462,222 +10705,228 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>46000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>103300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-68900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-26300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>162500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-57800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-48700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-99700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-59600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-126000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>413100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-144300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-29600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-43200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-87700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-62100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-14700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-29600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-105200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-111800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>256500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>9900</v>
-      </c>
-      <c r="AL100" s="3">
-        <v>2100</v>
       </c>
       <c r="AM100" s="3">
         <v>2100</v>
       </c>
       <c r="AN100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AO100" s="3">
         <v>3600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2300</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-100</v>
       </c>
       <c r="T101" s="3">
         <v>-100</v>
       </c>
       <c r="U101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
       <c r="AF101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AG101" s="3">
         <v>200</v>
       </c>
       <c r="AH101" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AI101" s="3">
         <v>0</v>
@@ -10700,123 +10949,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="E102" s="3">
         <v>71700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-53600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>24500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>28700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-45500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>36500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>28500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-30400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-29700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-175300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>61000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>80700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-167400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-895000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>472800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>224300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-14800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-387800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>491100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>412400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-36200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>56000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>23900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-28400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>13200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5000</v>
       </c>
-      <c r="AG102" s="3">
-        <v>0</v>
-      </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-63100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>65700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-136900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-22400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>28000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>16100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-2200</v>
       </c>
     </row>
